--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -458,16 +458,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>X3</v>
+        <v>CtrlRelay</v>
       </c>
       <c r="B2" t="str">
         <v>connector</v>
       </c>
       <c r="C2" t="str">
-        <v>90980-12326</v>
+        <v>89531-60010</v>
       </c>
       <c r="D2" t="str">
-        <v>Sumitomo</v>
+        <v>Toyota</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -485,7 +485,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -499,13 +499,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>X5; X6</v>
+        <v>X3</v>
       </c>
       <c r="B3" t="str">
         <v>connector</v>
       </c>
       <c r="C3" t="str">
-        <v>90980-12520</v>
+        <v>90980-12326</v>
       </c>
       <c r="D3" t="str">
         <v>Sumitomo</v>
@@ -514,7 +514,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="str">
         <v>ea</v>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -540,22 +540,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>X1</v>
+        <v>X5; X6</v>
       </c>
       <c r="B4" t="str">
         <v>connector</v>
       </c>
       <c r="C4" t="str">
-        <v>13669859</v>
+        <v>90980-12520</v>
       </c>
       <c r="D4" t="str">
-        <v>Aptiv</v>
+        <v>Sumitomo</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="str">
         <v>ea</v>
@@ -567,7 +567,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -581,13 +581,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>J1</v>
+        <v>X1</v>
       </c>
       <c r="B5" t="str">
         <v>connector</v>
       </c>
       <c r="C5" t="str">
-        <v>33511394</v>
+        <v>13669859</v>
       </c>
       <c r="D5" t="str">
         <v>Aptiv</v>
@@ -622,16 +622,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>X2</v>
+        <v>J1</v>
       </c>
       <c r="B6" t="str">
         <v>connector</v>
       </c>
       <c r="C6" t="str">
-        <v>HX040-6P</v>
+        <v>33511394</v>
       </c>
       <c r="D6" t="str">
-        <v>Sumitomo</v>
+        <v>Aptiv</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -649,7 +649,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -663,16 +663,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>X4</v>
+        <v>X2</v>
       </c>
       <c r="B7" t="str">
         <v>connector</v>
       </c>
       <c r="C7" t="str">
-        <v>LS600HL</v>
+        <v>HX040-6P</v>
       </c>
       <c r="D7" t="str">
-        <v>Lexus</v>
+        <v>Sumitomo</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -690,7 +690,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -704,22 +704,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; CAN1; CAN2; CanHI; CanLO; Chassis; DCDC-F; DCDC-R; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; Pos Fuse; Precharge Relay; Precharge Resistor; RearDtsch12-F; RearDtsch12-M; RT32; RT33; RT35; RT38; SENSE; Term; X7; X8; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X78; X79; X81; X82; X83; X84; X85; X86; X87; X88; X91; X93</v>
+        <v>X4</v>
       </c>
       <c r="B8" t="str">
         <v>connector</v>
       </c>
       <c r="C8" t="str">
-        <v>Unassigned</v>
+        <v>LS600HL</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>Lexus</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="G8" t="str">
         <v>ea</v>
@@ -731,7 +731,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -745,10 +745,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>X2.1_X1.45</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; CAN1; CAN2; CanHI; CanLO; CDL Motor; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; Pos Fuse; Precharge Relay; Precharge Resistor; RearDtsch12-F; RearDtsch12-M; RT32; RT33; RT35; RT38; SENSE; Term; X7; X8; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X78; X81; X82; X83; X84; X85; X86; X87; X88; X91; X93; X94; X95; X96; X97</v>
       </c>
       <c r="B9" t="str">
-        <v>wire</v>
+        <v>connector</v>
       </c>
       <c r="C9" t="str">
         <v>Unassigned</v>
@@ -760,19 +760,19 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="G9" t="str">
         <v>ea</v>
       </c>
       <c r="H9" t="str">
-        <v>20 AWG</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>YEBU</v>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>7</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -781,12 +781,12 @@
         <v/>
       </c>
       <c r="M9" t="str">
-        <v>X2.1_X1.45</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>J1.46_X2.2</v>
+        <v>X2.1_X1.45</v>
       </c>
       <c r="B10" t="str">
         <v>wire</v>
@@ -810,7 +810,7 @@
         <v>20 AWG</v>
       </c>
       <c r="I10" t="str">
-        <v>BNBU</v>
+        <v>YEBU</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -822,12 +822,12 @@
         <v/>
       </c>
       <c r="M10" t="str">
-        <v>J1.46_X2.2</v>
+        <v>X2.1_X1.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>X2.5_X1.47</v>
+        <v>J1.46_X2.2</v>
       </c>
       <c r="B11" t="str">
         <v>wire</v>
@@ -851,7 +851,7 @@
         <v>20 AWG</v>
       </c>
       <c r="I11" t="str">
-        <v>WHBU</v>
+        <v>BNBU</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -863,12 +863,12 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>X2.5_X1.47</v>
+        <v>J1.46_X2.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>J1.48_X2.3</v>
+        <v>X2.5_X1.47</v>
       </c>
       <c r="B12" t="str">
         <v>wire</v>
@@ -892,7 +892,7 @@
         <v>20 AWG</v>
       </c>
       <c r="I12" t="str">
-        <v>WHGN</v>
+        <v>WHBU</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -904,12 +904,12 @@
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>J1.48_X2.3</v>
+        <v>X2.5_X1.47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>FrontDtsch12-M.6_Precharge Relay.Coil-; FrontDtsch12-M.7_HV+ Contactor.Coil-; HV- Contactor.Coil-_RearDtsch12-M.7; HV+ Contactor.Coil+_X78.1; J1.39_X3.7; Precharge Relay.Coil+_X79.1; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
+        <v>J1.48_X2.3</v>
       </c>
       <c r="B13" t="str">
         <v>wire</v>
@@ -924,16 +924,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G13" t="str">
         <v>ea</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>20 AWG</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>WHGN</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -945,12 +945,12 @@
         <v/>
       </c>
       <c r="M13" t="str">
-        <v>FrontDtsch12-M.6_Precharge Relay.Coil-; FrontDtsch12-M.7_HV+ Contactor.Coil-; HV+ Contactor.Coil+_X78.1; HV- Contactor.Coil-_RearDtsch12-M.7; J1.39_X3.7; Precharge Relay.Coil+_X79.1; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
+        <v>J1.48_X2.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>J1.16_X4.34; J1.18_X4.13; J1.20_X4.2; J1.22_X4.22; X4.17_X5.3; X6.3_X4.38</v>
+        <v>EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; F13.OUT_F21.OUT; FrontDtsch12-M.6_Precharge Relay.Coil-; FrontDtsch12-M.7_HV+ Contactor.Coil-; HV- Contactor.Coil-_RearDtsch12-M.7; HV+ Contactor.Coil+_X78.1; J1.39_X3.7; Precharge Relay.Coil+_X95.1; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
       </c>
       <c r="B14" t="str">
         <v>wire</v>
@@ -965,16 +965,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G14" t="str">
         <v>ea</v>
       </c>
       <c r="H14" t="str">
-        <v>22 AWG</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>WH</v>
+        <v/>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -986,12 +986,12 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>J1.16_X4.34; J1.18_X4.13; J1.20_X4.2; J1.22_X4.22; X4.17_X5.3; X6.3_X4.38</v>
+        <v>EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; F13.OUT_F21.OUT; FrontDtsch12-M.6_Precharge Relay.Coil-; FrontDtsch12-M.7_HV+ Contactor.Coil-; HV+ Contactor.Coil+_X78.1; HV- Contactor.Coil-_RearDtsch12-M.7; J1.39_X3.7; Precharge Relay.Coil+_X95.1; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>J1.17_X4.35; J1.19_X4.14; J1.21_X4.3; J1.23_X4.23; X4.20_X5.1; X6.1_X4.40</v>
+        <v>J1.16_X4.34; J1.18_X4.13; J1.20_X4.2; J1.22_X4.22; X4.17_X5.3; X6.3_X4.38</v>
       </c>
       <c r="B15" t="str">
         <v>wire</v>
@@ -1015,7 +1015,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I15" t="str">
-        <v>BK</v>
+        <v>WH</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -1027,12 +1027,12 @@
         <v/>
       </c>
       <c r="M15" t="str">
-        <v>J1.17_X4.35; J1.19_X4.14; J1.21_X4.3; J1.23_X4.23; X4.20_X5.1; X6.1_X4.40</v>
+        <v>J1.16_X4.34; J1.18_X4.13; J1.20_X4.2; J1.22_X4.22; X4.17_X5.3; X6.3_X4.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>X4.18_X5.2; X6.2_X4.39</v>
+        <v>J1.17_X4.35; J1.19_X4.14; J1.21_X4.3; J1.23_X4.23; X4.20_X5.1; X6.1_X4.40</v>
       </c>
       <c r="B16" t="str">
         <v>wire</v>
@@ -1047,7 +1047,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G16" t="str">
         <v>ea</v>
@@ -1056,7 +1056,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I16" t="str">
-        <v>BU</v>
+        <v>BK</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1068,12 +1068,12 @@
         <v/>
       </c>
       <c r="M16" t="str">
-        <v>X4.18_X5.2; X6.2_X4.39</v>
+        <v>J1.17_X4.35; J1.19_X4.14; J1.21_X4.3; J1.23_X4.23; X4.20_X5.1; X6.1_X4.40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>X4.9_X5.5; X6.5_X4.27</v>
+        <v>X4.18_X5.2; X6.2_X4.39</v>
       </c>
       <c r="B17" t="str">
         <v>wire</v>
@@ -1097,7 +1097,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I17" t="str">
-        <v>GN</v>
+        <v>BU</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1109,12 +1109,12 @@
         <v/>
       </c>
       <c r="M17" t="str">
-        <v>X4.9_X5.5; X6.5_X4.27</v>
+        <v>X4.18_X5.2; X6.2_X4.39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>X4.7_X5.6; X6.6_X4.29</v>
+        <v>X4.9_X5.5; X6.5_X4.27</v>
       </c>
       <c r="B18" t="str">
         <v>wire</v>
@@ -1138,7 +1138,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I18" t="str">
-        <v>RD</v>
+        <v>GN</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1150,12 +1150,12 @@
         <v/>
       </c>
       <c r="M18" t="str">
-        <v>X4.7_X5.6; X6.6_X4.29</v>
+        <v>X4.9_X5.5; X6.5_X4.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>X4.6_X5.7; X6.7_X4.28</v>
+        <v>X4.7_X5.6; X6.6_X4.29</v>
       </c>
       <c r="B19" t="str">
         <v>wire</v>
@@ -1179,7 +1179,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I19" t="str">
-        <v>YE</v>
+        <v>RD</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1191,12 +1191,12 @@
         <v/>
       </c>
       <c r="M19" t="str">
-        <v>X4.6_X5.7; X6.7_X4.28</v>
+        <v>X4.7_X5.6; X6.6_X4.29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85; GndCtrl.3_K19.85; GndCtrl.4_K20.85; GndCtrl.5_K12.85; X4.30_X7.6</v>
+        <v>X4.6_X5.7; X6.7_X4.28</v>
       </c>
       <c r="B20" t="str">
         <v>wire</v>
@@ -1211,16 +1211,16 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G20" t="str">
         <v>ea</v>
       </c>
       <c r="H20" t="str">
-        <v>18 AWG</v>
+        <v>22 AWG</v>
       </c>
       <c r="I20" t="str">
-        <v>BK</v>
+        <v>YE</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1232,12 +1232,12 @@
         <v/>
       </c>
       <c r="M20" t="str">
-        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85; GndCtrl.3_K19.85; GndCtrl.4_K20.85; GndCtrl.5_K12.85; X4.30_X7.6</v>
+        <v>X4.6_X5.7; X6.7_X4.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; Bat+.10_K12.30; X7.5_X8</v>
+        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85; GndCtrl.3_K19.85; GndCtrl.4_K20.85; GndCtrl.5_K12.85; X4.30_X7.6</v>
       </c>
       <c r="B21" t="str">
         <v>wire</v>
@@ -1258,10 +1258,10 @@
         <v>ea</v>
       </c>
       <c r="H21" t="str">
-        <v>14 AWG</v>
+        <v>18 AWG</v>
       </c>
       <c r="I21" t="str">
-        <v>RD</v>
+        <v>BK</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1273,12 +1273,12 @@
         <v/>
       </c>
       <c r="M21" t="str">
-        <v>Bat+.10_K12.30; Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; X7.5_X8</v>
+        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85; GndCtrl.3_K19.85; GndCtrl.4_K20.85; GndCtrl.5_K12.85; X4.30_X7.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>K11.87_F11.IN; K12.87_F12.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
+        <v>Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; Bat+.10_K12.30; X7.5_X8</v>
       </c>
       <c r="B22" t="str">
         <v>wire</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" t="str">
         <v>ea</v>
@@ -1302,7 +1302,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>RD</v>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1314,12 +1314,12 @@
         <v/>
       </c>
       <c r="M22" t="str">
-        <v>K11.87_F11.IN; K12.87_F12.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
+        <v>Bat+.10_K12.30; Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; X7.5_X8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
+        <v>K11.87_F11.IN; K12.87_F12.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
       </c>
       <c r="B23" t="str">
         <v>wire</v>
@@ -1334,16 +1334,16 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G23" t="str">
         <v>ea</v>
       </c>
       <c r="H23" t="str">
-        <v>18 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I23" t="str">
-        <v>OG</v>
+        <v/>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1355,12 +1355,12 @@
         <v/>
       </c>
       <c r="M23" t="str">
-        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
+        <v>K11.87_F11.IN; K12.87_F12.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>BatCtrl.2_K18.86; BatCtrl.3_K19.86; BatCtrl.4_K20.86; BatCtrl.5_K12.86</v>
+        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
       </c>
       <c r="B24" t="str">
         <v>wire</v>
@@ -1375,7 +1375,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" t="str">
         <v>ea</v>
@@ -1384,7 +1384,7 @@
         <v>18 AWG</v>
       </c>
       <c r="I24" t="str">
-        <v>RD</v>
+        <v>OG</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1396,12 +1396,12 @@
         <v/>
       </c>
       <c r="M24" t="str">
-        <v>BatCtrl.2_K18.86; BatCtrl.3_K19.86; BatCtrl.4_K20.86; BatCtrl.5_K12.86</v>
+        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>DCDC-F.1_FrontDtsch12-M.1; DCDC-R.1_RearDtsch12-M.1; FrontDtsch12-F.1_RearDtsch12-F.1</v>
+        <v>BatCtrl.2_K18.86; BatCtrl.3_K19.86; BatCtrl.4_K20.86; BatCtrl.5_K12.86</v>
       </c>
       <c r="B25" t="str">
         <v>wire</v>
@@ -1416,16 +1416,16 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" t="str">
         <v>ea</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>18 AWG</v>
       </c>
       <c r="I25" t="str">
-        <v>BK</v>
+        <v>RD</v>
       </c>
       <c r="J25" t="str">
         <v/>
@@ -1437,12 +1437,12 @@
         <v/>
       </c>
       <c r="M25" t="str">
-        <v>DCDC-F.1_FrontDtsch12-M.1; DCDC-R.1_RearDtsch12-M.1; FrontDtsch12-F.1_RearDtsch12-F.1</v>
+        <v>BatCtrl.2_K18.86; BatCtrl.3_K19.86; BatCtrl.4_K20.86; BatCtrl.5_K12.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2</v>
+        <v>DCDC-F.1_FrontDtsch12-M.1; DCDC-R.1_RearDtsch12-M.1; FrontDtsch12-F.1_RearDtsch12-F.1</v>
       </c>
       <c r="B26" t="str">
         <v>wire</v>
@@ -1457,7 +1457,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="str">
         <v>ea</v>
@@ -1466,7 +1466,7 @@
         <v/>
       </c>
       <c r="I26" t="str">
-        <v>WH</v>
+        <v>BK</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -1478,12 +1478,12 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2</v>
+        <v>DCDC-F.1_FrontDtsch12-M.1; DCDC-R.1_RearDtsch12-M.1; FrontDtsch12-F.1_RearDtsch12-F.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>BMS-F.4_CanLO.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1</v>
+        <v>FrontDtsch12-F.2_RearDtsch12-F.2</v>
       </c>
       <c r="B27" t="str">
         <v>wire</v>
@@ -1498,7 +1498,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G27" t="str">
         <v>ea</v>
@@ -1507,7 +1507,7 @@
         <v/>
       </c>
       <c r="I27" t="str">
-        <v>GN</v>
+        <v>WH</v>
       </c>
       <c r="J27" t="str">
         <v/>
@@ -1519,12 +1519,12 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v>BMS-F.4_CanLO.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1</v>
+        <v>FrontDtsch12-F.2_RearDtsch12-F.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
+        <v>BMS-F.4_CanLO.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1539,7 +1539,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G28" t="str">
         <v>ea</v>
@@ -1548,7 +1548,7 @@
         <v/>
       </c>
       <c r="I28" t="str">
-        <v>WHBU</v>
+        <v>GN</v>
       </c>
       <c r="J28" t="str">
         <v/>
@@ -1560,12 +1560,12 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
+        <v>BMS-F.4_CanLO.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>FrontDtsch12-F.5_RearDtsch12-F.5</v>
+        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
       </c>
       <c r="B29" t="str">
         <v>wire</v>
@@ -1589,7 +1589,7 @@
         <v/>
       </c>
       <c r="I29" t="str">
-        <v>BU</v>
+        <v>WHBU</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -1601,12 +1601,12 @@
         <v/>
       </c>
       <c r="M29" t="str">
-        <v>FrontDtsch12-F.5_RearDtsch12-F.5</v>
+        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
+        <v>FrontDtsch12-F.5_RearDtsch12-F.5</v>
       </c>
       <c r="B30" t="str">
         <v>wire</v>
@@ -1630,7 +1630,7 @@
         <v/>
       </c>
       <c r="I30" t="str">
-        <v>WHBN</v>
+        <v>BU</v>
       </c>
       <c r="J30" t="str">
         <v/>
@@ -1642,12 +1642,12 @@
         <v/>
       </c>
       <c r="M30" t="str">
-        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
+        <v>FrontDtsch12-F.5_RearDtsch12-F.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7</v>
+        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
       </c>
       <c r="B31" t="str">
         <v>wire</v>
@@ -1671,7 +1671,7 @@
         <v/>
       </c>
       <c r="I31" t="str">
-        <v>BN</v>
+        <v>WHBN</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1683,12 +1683,12 @@
         <v/>
       </c>
       <c r="M31" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7</v>
+        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>FrontDtsch12-F.8_RearDtsch12-F.8</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7</v>
       </c>
       <c r="B32" t="str">
         <v>wire</v>
@@ -1712,7 +1712,7 @@
         <v/>
       </c>
       <c r="I32" t="str">
-        <v>OG</v>
+        <v>BN</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1724,12 +1724,12 @@
         <v/>
       </c>
       <c r="M32" t="str">
-        <v>FrontDtsch12-F.8_RearDtsch12-F.8</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
+        <v>FrontDtsch12-F.8_RearDtsch12-F.8</v>
       </c>
       <c r="B33" t="str">
         <v>wire</v>
@@ -1753,7 +1753,7 @@
         <v/>
       </c>
       <c r="I33" t="str">
-        <v>WHOG</v>
+        <v>OG</v>
       </c>
       <c r="J33" t="str">
         <v/>
@@ -1765,12 +1765,12 @@
         <v/>
       </c>
       <c r="M33" t="str">
-        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
+        <v>FrontDtsch12-F.8_RearDtsch12-F.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
+        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
       </c>
       <c r="B34" t="str">
         <v>wire</v>
@@ -1794,7 +1794,7 @@
         <v/>
       </c>
       <c r="I34" t="str">
-        <v>WHGN</v>
+        <v>WHOG</v>
       </c>
       <c r="J34" t="str">
         <v/>
@@ -1806,12 +1806,12 @@
         <v/>
       </c>
       <c r="M34" t="str">
-        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
+        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>DCDC-F.2_FrontDtsch12-M.12; DCDC-R.2_RearDtsch12-M.12; FrontDtsch12-F.12_RearDtsch12-F.12; HV- Contactor.Coil+_X91.1; J1.15_F11.OUT</v>
+        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
       </c>
       <c r="B35" t="str">
         <v>wire</v>
@@ -1826,7 +1826,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G35" t="str">
         <v>ea</v>
@@ -1835,7 +1835,7 @@
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>RD</v>
+        <v>WHGN</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -1847,12 +1847,12 @@
         <v/>
       </c>
       <c r="M35" t="str">
-        <v>DCDC-F.2_FrontDtsch12-M.12; DCDC-R.2_RearDtsch12-M.12; FrontDtsch12-F.12_RearDtsch12-F.12; HV- Contactor.Coil+_X91.1; J1.15_F11.OUT</v>
+        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>K17.86_X76.1</v>
+        <v>DCDC-F.2_FrontDtsch12-M.12; DCDC-R.2_RearDtsch12-M.12; FrontDtsch12-F.12_RearDtsch12-F.12; HV- Contactor.Coil+_X91.1; J1.15_F11.OUT</v>
       </c>
       <c r="B36" t="str">
         <v>wire</v>
@@ -1867,13 +1867,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G36" t="str">
         <v>ea</v>
       </c>
       <c r="H36" t="str">
-        <v>16 AWG</v>
+        <v/>
       </c>
       <c r="I36" t="str">
         <v>RD</v>
@@ -1888,12 +1888,12 @@
         <v/>
       </c>
       <c r="M36" t="str">
-        <v>K17.86_X76.1</v>
+        <v>DCDC-F.2_FrontDtsch12-M.12; DCDC-R.2_RearDtsch12-M.12; FrontDtsch12-F.12_RearDtsch12-F.12; HV- Contactor.Coil+_X91.1; J1.15_F11.OUT</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
+        <v>F22.IN_X97.1; F22.OUT_X1.56; K17.86_X76.1</v>
       </c>
       <c r="B37" t="str">
         <v>wire</v>
@@ -1914,10 +1914,10 @@
         <v>ea</v>
       </c>
       <c r="H37" t="str">
-        <v>3/0 AWG</v>
+        <v>16 AWG</v>
       </c>
       <c r="I37" t="str">
-        <v>OGRD</v>
+        <v>RD</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -1929,12 +1929,12 @@
         <v/>
       </c>
       <c r="M37" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
+        <v>F22.IN_X97.1; F22.OUT_X1.56; K17.86_X76.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>NET_mnnbwso0_7</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
       </c>
       <c r="B38" t="str">
         <v>wire</v>
@@ -1949,16 +1949,16 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G38" t="str">
         <v>ea</v>
       </c>
       <c r="H38" t="str">
-        <v>20 AWG</v>
+        <v>3/0 AWG</v>
       </c>
       <c r="I38" t="str">
-        <v>RD</v>
+        <v>OGRD</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -1970,12 +1970,12 @@
         <v/>
       </c>
       <c r="M38" t="str">
-        <v>NET_mnnbwso0_7</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>NET_mnnb3cvb_4</v>
+        <v>NET_mnnbwso0_7</v>
       </c>
       <c r="B39" t="str">
         <v>wire</v>
@@ -1996,10 +1996,10 @@
         <v>ea</v>
       </c>
       <c r="H39" t="str">
-        <v>14 AWG</v>
+        <v>20 AWG</v>
       </c>
       <c r="I39" t="str">
-        <v>OGRD</v>
+        <v>RD</v>
       </c>
       <c r="J39" t="str">
         <v/>
@@ -2011,12 +2011,12 @@
         <v/>
       </c>
       <c r="M39" t="str">
-        <v>NET_mnnb3cvb_4</v>
+        <v>NET_mnnbwso0_7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
+        <v>NET_mnnb3cvb_4</v>
       </c>
       <c r="B40" t="str">
         <v>wire</v>
@@ -2031,13 +2031,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="str">
         <v>ea</v>
       </c>
       <c r="H40" t="str">
-        <v>16 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I40" t="str">
         <v>OGRD</v>
@@ -2052,12 +2052,12 @@
         <v/>
       </c>
       <c r="M40" t="str">
-        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
+        <v>NET_mnnb3cvb_4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HV Bat Front.V-_X84.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Neg Fuse.OUT_X85.1</v>
+        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
       </c>
       <c r="B41" t="str">
         <v>wire</v>
@@ -2072,16 +2072,16 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G41" t="str">
         <v>ea</v>
       </c>
       <c r="H41" t="str">
-        <v>3/0 AWG</v>
+        <v>16 AWG</v>
       </c>
       <c r="I41" t="str">
-        <v>OGBK</v>
+        <v>OGRD</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -2093,12 +2093,12 @@
         <v/>
       </c>
       <c r="M41" t="str">
-        <v>HV Bat Front.V-_X84.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Neg Fuse.OUT_X85.1</v>
+        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Neg Fuse.OUT_X85.1</v>
+        <v>HV Bat Front.V-_X84.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Neg Fuse.OUT_X85.1</v>
       </c>
       <c r="B42" t="str">
         <v>wire</v>
@@ -2113,13 +2113,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G42" t="str">
         <v>ea</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>3/0 AWG</v>
       </c>
       <c r="I42" t="str">
         <v>OGBK</v>
@@ -2134,12 +2134,12 @@
         <v/>
       </c>
       <c r="M42" t="str">
-        <v>Neg Fuse.OUT_X85.1</v>
+        <v>HV Bat Front.V-_X84.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Neg Fuse.OUT_X85.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
+        <v>Neg Fuse.OUT_X85.1</v>
       </c>
       <c r="B43" t="str">
         <v>wire</v>
@@ -2154,7 +2154,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" t="str">
         <v>ea</v>
@@ -2163,7 +2163,7 @@
         <v/>
       </c>
       <c r="I43" t="str">
-        <v>WHRD</v>
+        <v>OGBK</v>
       </c>
       <c r="J43" t="str">
         <v/>
@@ -2175,12 +2175,12 @@
         <v/>
       </c>
       <c r="M43" t="str">
-        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
+        <v>Neg Fuse.OUT_X85.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
+        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
       </c>
       <c r="B44" t="str">
         <v>wire</v>
@@ -2204,7 +2204,7 @@
         <v/>
       </c>
       <c r="I44" t="str">
-        <v>RDWH</v>
+        <v>WHRD</v>
       </c>
       <c r="J44" t="str">
         <v/>
@@ -2216,12 +2216,12 @@
         <v/>
       </c>
       <c r="M44" t="str">
-        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
+        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BMS-F.3_CanHI.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1</v>
+        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
       </c>
       <c r="B45" t="str">
         <v>wire</v>
@@ -2236,7 +2236,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G45" t="str">
         <v>ea</v>
@@ -2245,7 +2245,7 @@
         <v/>
       </c>
       <c r="I45" t="str">
-        <v>YE</v>
+        <v>RDWH</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -2257,12 +2257,12 @@
         <v/>
       </c>
       <c r="M45" t="str">
-        <v>BMS-F.3_CanHI.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1</v>
+        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
+        <v>BMS-F.3_CanHI.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1</v>
       </c>
       <c r="B46" t="str">
         <v>wire</v>
@@ -2277,16 +2277,16 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G46" t="str">
         <v>ea</v>
       </c>
       <c r="H46" t="str">
-        <v>12 AWG</v>
+        <v/>
       </c>
       <c r="I46" t="str">
-        <v>BK</v>
+        <v>YE</v>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -2298,12 +2298,12 @@
         <v/>
       </c>
       <c r="M46" t="str">
-        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
+        <v>BMS-F.3_CanHI.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>F13.OUT_OilPump.5</v>
+        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
       </c>
       <c r="B47" t="str">
         <v>wire</v>
@@ -2318,7 +2318,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="str">
         <v>ea</v>
@@ -2327,7 +2327,7 @@
         <v>12 AWG</v>
       </c>
       <c r="I47" t="str">
-        <v>BU</v>
+        <v>BK</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -2339,53 +2339,135 @@
         <v/>
       </c>
       <c r="M47" t="str">
-        <v>F13.OUT_OilPump.5</v>
+        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
+        <v>F13.OUT_F21.OUT</v>
+      </c>
+      <c r="B48" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>1</v>
+      </c>
+      <c r="G48" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H48" t="str">
+        <v>12 AWG</v>
+      </c>
+      <c r="I48" t="str">
+        <v>BU</v>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v>F13.OUT_F21.OUT</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>F21.IN_X96.1</v>
+      </c>
+      <c r="B49" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>1</v>
+      </c>
+      <c r="G49" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H49" t="str">
+        <v>12 AWG</v>
+      </c>
+      <c r="I49" t="str">
+        <v>RD</v>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v>F21.IN_X96.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
         <v>10863985</v>
       </c>
-      <c r="B48" t="str">
+      <c r="B50" t="str">
         <v>contact</v>
       </c>
-      <c r="C48" t="str">
+      <c r="C50" t="str">
         <v>10863985</v>
       </c>
-      <c r="D48" t="str">
+      <c r="D50" t="str">
         <v>Aptiv</v>
       </c>
-      <c r="E48" t="str">
-        <v/>
-      </c>
-      <c r="F48" t="str">
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
         <v>10</v>
       </c>
-      <c r="G48" t="str">
-        <v>ea</v>
-      </c>
-      <c r="H48" t="str">
-        <v/>
-      </c>
-      <c r="I48" t="str">
-        <v/>
-      </c>
-      <c r="J48" t="str">
-        <v/>
-      </c>
-      <c r="K48" t="str">
-        <v/>
-      </c>
-      <c r="L48" t="str">
-        <v/>
-      </c>
-      <c r="M48" t="str">
+      <c r="G50" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2437,7 +2519,7 @@
         <v>Total Connectors</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -2445,7 +2527,7 @@
         <v>Total Wires</v>
       </c>
       <c r="B9">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -2461,7 +2543,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>4/18/2026, 1:19:42 PM</v>
+        <v>4/20/2026, 11:26:10 AM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M54"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -745,7 +745,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; CAN1; CAN2; CanHI; CanLO; CDL Motor; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; Pos Fuse; Precharge Relay; Precharge Resistor; RearDtsch12-F; RearDtsch12-M; RT32; RT33; RT35; RT38; SENSE; Term; X7; X8; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X78; X81; X82; X83; X84; X85; X86; X87; X88; X91; X93; X94; X95; X96; X97</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDL Motor; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X7; X8; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X81; X82; X83; X84; X85; X86; X87; X88; X93; X95; X96; X97; X98; X99; X100; X101; X102; X103; X104</v>
       </c>
       <c r="B9" t="str">
         <v>connector</v>
@@ -760,7 +760,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G9" t="str">
         <v>ea</v>
@@ -950,7 +950,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; F13.OUT_F21.OUT; FrontDtsch12-M.6_Precharge Relay.Coil-; FrontDtsch12-M.7_HV+ Contactor.Coil-; HV- Contactor.Coil-_RearDtsch12-M.7; HV+ Contactor.Coil+_X78.1; J1.39_X3.7; Precharge Relay.Coil+_X95.1; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
+        <v>EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; F13.OUT_F21.OUT; F23.IN_X104.1; FrontDtsch12-M.6_Precharge Relay.Coil-; FrontDtsch12-M.7_HV+ Contactor.Coil-; HV- Contactor.Coil-_RearDtsch12-M.7; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
       </c>
       <c r="B14" t="str">
         <v>wire</v>
@@ -986,7 +986,7 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; F13.OUT_F21.OUT; FrontDtsch12-M.6_Precharge Relay.Coil-; FrontDtsch12-M.7_HV+ Contactor.Coil-; HV+ Contactor.Coil+_X78.1; HV- Contactor.Coil-_RearDtsch12-M.7; J1.39_X3.7; Precharge Relay.Coil+_X95.1; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
+        <v>EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; F13.OUT_F21.OUT; F23.IN_X104.1; FrontDtsch12-M.6_Precharge Relay.Coil-; FrontDtsch12-M.7_HV+ Contactor.Coil-; HV- Contactor.Coil-_RearDtsch12-M.7; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
       </c>
     </row>
     <row r="15">
@@ -1237,7 +1237,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85; GndCtrl.3_K19.85; GndCtrl.4_K20.85; GndCtrl.5_K12.85; X4.30_X7.6</v>
+        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85; X4.30_X7.6</v>
       </c>
       <c r="B21" t="str">
         <v>wire</v>
@@ -1252,7 +1252,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G21" t="str">
         <v>ea</v>
@@ -1273,7 +1273,7 @@
         <v/>
       </c>
       <c r="M21" t="str">
-        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85; GndCtrl.3_K19.85; GndCtrl.4_K20.85; GndCtrl.5_K12.85; X4.30_X7.6</v>
+        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85; X4.30_X7.6</v>
       </c>
     </row>
     <row r="22">
@@ -1384,7 +1384,7 @@
         <v>18 AWG</v>
       </c>
       <c r="I24" t="str">
-        <v>OG</v>
+        <v>VT</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1401,7 +1401,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>BatCtrl.2_K18.86; BatCtrl.3_K19.86; BatCtrl.4_K20.86; BatCtrl.5_K12.86</v>
+        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86; BatCtrl.5_K12.86</v>
       </c>
       <c r="B25" t="str">
         <v>wire</v>
@@ -1416,7 +1416,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" t="str">
         <v>ea</v>
@@ -1437,12 +1437,12 @@
         <v/>
       </c>
       <c r="M25" t="str">
-        <v>BatCtrl.2_K18.86; BatCtrl.3_K19.86; BatCtrl.4_K20.86; BatCtrl.5_K12.86</v>
+        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86; BatCtrl.5_K12.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>DCDC-F.1_FrontDtsch12-M.1; DCDC-R.1_RearDtsch12-M.1; FrontDtsch12-F.1_RearDtsch12-F.1</v>
+        <v>DCDC-F.1_FrontDtsch12-M.1; DCDC-R.1_RearDtsch12-M.1; FrontDtsch12-F.1_RearDtsch12-F.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.3_X98.1; PBCtrl.6_GrnLed.2</v>
       </c>
       <c r="B26" t="str">
         <v>wire</v>
@@ -1457,7 +1457,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G26" t="str">
         <v>ea</v>
@@ -1478,7 +1478,7 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v>DCDC-F.1_FrontDtsch12-M.1; DCDC-R.1_RearDtsch12-M.1; FrontDtsch12-F.1_RearDtsch12-F.1</v>
+        <v>DCDC-F.1_FrontDtsch12-M.1; DCDC-R.1_RearDtsch12-M.1; FrontDtsch12-F.1_RearDtsch12-F.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.3_X98.1; PBCtrl.6_GrnLed.2</v>
       </c>
     </row>
     <row r="27">
@@ -1524,7 +1524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>BMS-F.4_CanLO.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1</v>
+        <v>BMS-F.4_CanLO.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; PBCtrl.7_GrnLed.1</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1539,7 +1539,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" t="str">
         <v>ea</v>
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>BMS-F.4_CanLO.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1</v>
+        <v>BMS-F.4_CanLO.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; PBCtrl.7_GrnLed.1</v>
       </c>
     </row>
     <row r="29">
@@ -1688,7 +1688,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_PkBrk.1</v>
       </c>
       <c r="B32" t="str">
         <v>wire</v>
@@ -1703,7 +1703,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="str">
         <v>ea</v>
@@ -1724,7 +1724,7 @@
         <v/>
       </c>
       <c r="M32" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_PkBrk.1</v>
       </c>
     </row>
     <row r="33">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>DCDC-F.2_FrontDtsch12-M.12; DCDC-R.2_RearDtsch12-M.12; FrontDtsch12-F.12_RearDtsch12-F.12; HV- Contactor.Coil+_X91.1; J1.15_F11.OUT</v>
+        <v>DCDC-F.2_FrontDtsch12-M.12; DCDC-R.2_RearDtsch12-M.12; FrontDtsch12-F.12_RearDtsch12-F.12; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1</v>
       </c>
       <c r="B36" t="str">
         <v>wire</v>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G36" t="str">
         <v>ea</v>
@@ -1888,12 +1888,12 @@
         <v/>
       </c>
       <c r="M36" t="str">
-        <v>DCDC-F.2_FrontDtsch12-M.12; DCDC-R.2_RearDtsch12-M.12; FrontDtsch12-F.12_RearDtsch12-F.12; HV- Contactor.Coil+_X91.1; J1.15_F11.OUT</v>
+        <v>DCDC-F.2_FrontDtsch12-M.12; DCDC-R.2_RearDtsch12-M.12; FrontDtsch12-F.12_RearDtsch12-F.12; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>F22.IN_X97.1; F22.OUT_X1.56; K17.86_X76.1</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
       </c>
       <c r="B37" t="str">
         <v>wire</v>
@@ -1914,10 +1914,10 @@
         <v>ea</v>
       </c>
       <c r="H37" t="str">
-        <v>16 AWG</v>
+        <v>3/0 AWG</v>
       </c>
       <c r="I37" t="str">
-        <v>RD</v>
+        <v>OGRD</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -1929,12 +1929,12 @@
         <v/>
       </c>
       <c r="M37" t="str">
-        <v>F22.IN_X97.1; F22.OUT_X1.56; K17.86_X76.1</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
+        <v>NET_mnnbwso0_7</v>
       </c>
       <c r="B38" t="str">
         <v>wire</v>
@@ -1949,16 +1949,16 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G38" t="str">
         <v>ea</v>
       </c>
       <c r="H38" t="str">
-        <v>3/0 AWG</v>
+        <v>20 AWG</v>
       </c>
       <c r="I38" t="str">
-        <v>OGRD</v>
+        <v>RD</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -1970,12 +1970,12 @@
         <v/>
       </c>
       <c r="M38" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
+        <v>NET_mnnbwso0_7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>NET_mnnbwso0_7</v>
+        <v>NET_mnnb3cvb_4</v>
       </c>
       <c r="B39" t="str">
         <v>wire</v>
@@ -1996,10 +1996,10 @@
         <v>ea</v>
       </c>
       <c r="H39" t="str">
-        <v>20 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I39" t="str">
-        <v>RD</v>
+        <v>OGRD</v>
       </c>
       <c r="J39" t="str">
         <v/>
@@ -2011,12 +2011,12 @@
         <v/>
       </c>
       <c r="M39" t="str">
-        <v>NET_mnnbwso0_7</v>
+        <v>NET_mnnb3cvb_4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>NET_mnnb3cvb_4</v>
+        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
       </c>
       <c r="B40" t="str">
         <v>wire</v>
@@ -2031,13 +2031,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" t="str">
         <v>ea</v>
       </c>
       <c r="H40" t="str">
-        <v>14 AWG</v>
+        <v>16 AWG</v>
       </c>
       <c r="I40" t="str">
         <v>OGRD</v>
@@ -2052,12 +2052,12 @@
         <v/>
       </c>
       <c r="M40" t="str">
-        <v>NET_mnnb3cvb_4</v>
+        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
+        <v>HV Bat Front.V-_X84.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Neg Fuse.OUT_X85.1</v>
       </c>
       <c r="B41" t="str">
         <v>wire</v>
@@ -2072,16 +2072,16 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" t="str">
         <v>ea</v>
       </c>
       <c r="H41" t="str">
-        <v>16 AWG</v>
+        <v>3/0 AWG</v>
       </c>
       <c r="I41" t="str">
-        <v>OGRD</v>
+        <v>OGBK</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -2093,12 +2093,12 @@
         <v/>
       </c>
       <c r="M41" t="str">
-        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
+        <v>HV Bat Front.V-_X84.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Neg Fuse.OUT_X85.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>HV Bat Front.V-_X84.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Neg Fuse.OUT_X85.1</v>
+        <v>Neg Fuse.OUT_X85.1</v>
       </c>
       <c r="B42" t="str">
         <v>wire</v>
@@ -2113,13 +2113,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G42" t="str">
         <v>ea</v>
       </c>
       <c r="H42" t="str">
-        <v>3/0 AWG</v>
+        <v/>
       </c>
       <c r="I42" t="str">
         <v>OGBK</v>
@@ -2134,12 +2134,12 @@
         <v/>
       </c>
       <c r="M42" t="str">
-        <v>HV Bat Front.V-_X84.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Neg Fuse.OUT_X85.1</v>
+        <v>Neg Fuse.OUT_X85.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Neg Fuse.OUT_X85.1</v>
+        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
       </c>
       <c r="B43" t="str">
         <v>wire</v>
@@ -2154,7 +2154,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" t="str">
         <v>ea</v>
@@ -2163,7 +2163,7 @@
         <v/>
       </c>
       <c r="I43" t="str">
-        <v>OGBK</v>
+        <v>WHRD</v>
       </c>
       <c r="J43" t="str">
         <v/>
@@ -2175,12 +2175,12 @@
         <v/>
       </c>
       <c r="M43" t="str">
-        <v>Neg Fuse.OUT_X85.1</v>
+        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
+        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
       </c>
       <c r="B44" t="str">
         <v>wire</v>
@@ -2204,7 +2204,7 @@
         <v/>
       </c>
       <c r="I44" t="str">
-        <v>WHRD</v>
+        <v>RDWH</v>
       </c>
       <c r="J44" t="str">
         <v/>
@@ -2216,12 +2216,12 @@
         <v/>
       </c>
       <c r="M44" t="str">
-        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
+        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
+        <v>BMS-F.3_CanHI.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1</v>
       </c>
       <c r="B45" t="str">
         <v>wire</v>
@@ -2236,7 +2236,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G45" t="str">
         <v>ea</v>
@@ -2245,7 +2245,7 @@
         <v/>
       </c>
       <c r="I45" t="str">
-        <v>RDWH</v>
+        <v>YE</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -2257,12 +2257,12 @@
         <v/>
       </c>
       <c r="M45" t="str">
-        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
+        <v>BMS-F.3_CanHI.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>BMS-F.3_CanHI.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1</v>
+        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
       </c>
       <c r="B46" t="str">
         <v>wire</v>
@@ -2277,16 +2277,16 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G46" t="str">
         <v>ea</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>12 AWG</v>
       </c>
       <c r="I46" t="str">
-        <v>YE</v>
+        <v>BK</v>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -2298,12 +2298,12 @@
         <v/>
       </c>
       <c r="M46" t="str">
-        <v>BMS-F.3_CanHI.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1</v>
+        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
+        <v>F13.OUT_F21.OUT</v>
       </c>
       <c r="B47" t="str">
         <v>wire</v>
@@ -2318,7 +2318,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" t="str">
         <v>ea</v>
@@ -2327,7 +2327,7 @@
         <v>12 AWG</v>
       </c>
       <c r="I47" t="str">
-        <v>BK</v>
+        <v>BU</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -2339,12 +2339,12 @@
         <v/>
       </c>
       <c r="M47" t="str">
-        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
+        <v>F13.OUT_F21.OUT</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>F13.OUT_F21.OUT</v>
+        <v>Precharge Relay.Coil+_X95.1</v>
       </c>
       <c r="B48" t="str">
         <v>wire</v>
@@ -2365,10 +2365,10 @@
         <v>ea</v>
       </c>
       <c r="H48" t="str">
-        <v>12 AWG</v>
+        <v>16 AWG</v>
       </c>
       <c r="I48" t="str">
-        <v>BU</v>
+        <v>VT</v>
       </c>
       <c r="J48" t="str">
         <v/>
@@ -2380,7 +2380,7 @@
         <v/>
       </c>
       <c r="M48" t="str">
-        <v>F13.OUT_F21.OUT</v>
+        <v>Precharge Relay.Coil+_X95.1</v>
       </c>
     </row>
     <row r="49">
@@ -2426,48 +2426,212 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
+        <v>F22.IN_X97.1; F22.OUT_X1.56</v>
+      </c>
+      <c r="B50" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>2</v>
+      </c>
+      <c r="G50" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H50" t="str">
+        <v>16 AWG</v>
+      </c>
+      <c r="I50" t="str">
+        <v>RD</v>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v>F22.IN_X97.1; F22.OUT_X1.56</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>PBCtrl.1_Caliper.1</v>
+      </c>
+      <c r="B51" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>1</v>
+      </c>
+      <c r="G51" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H51" t="str">
+        <v>14 AWG</v>
+      </c>
+      <c r="I51" t="str">
+        <v>WH</v>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v>PBCtrl.1_Caliper.1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>PBCtrl.2_Caliper.2</v>
+      </c>
+      <c r="B52" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>1</v>
+      </c>
+      <c r="G52" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H52" t="str">
+        <v>14 AWG</v>
+      </c>
+      <c r="I52" t="str">
+        <v>YE</v>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v>PBCtrl.2_Caliper.2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>PBCtrl.4_F23.OUT</v>
+      </c>
+      <c r="B53" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>1</v>
+      </c>
+      <c r="G53" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>VT</v>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v>PBCtrl.4_F23.OUT</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
         <v>10863985</v>
       </c>
-      <c r="B50" t="str">
+      <c r="B54" t="str">
         <v>contact</v>
       </c>
-      <c r="C50" t="str">
+      <c r="C54" t="str">
         <v>10863985</v>
       </c>
-      <c r="D50" t="str">
+      <c r="D54" t="str">
         <v>Aptiv</v>
       </c>
-      <c r="E50" t="str">
-        <v/>
-      </c>
-      <c r="F50" t="str">
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
         <v>10</v>
       </c>
-      <c r="G50" t="str">
-        <v>ea</v>
-      </c>
-      <c r="H50" t="str">
-        <v/>
-      </c>
-      <c r="I50" t="str">
-        <v/>
-      </c>
-      <c r="J50" t="str">
-        <v/>
-      </c>
-      <c r="K50" t="str">
-        <v/>
-      </c>
-      <c r="L50" t="str">
-        <v/>
-      </c>
-      <c r="M50" t="str">
+      <c r="G54" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M54"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2527,7 +2691,7 @@
         <v>Total Wires</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -2543,7 +2707,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>4/20/2026, 11:26:10 AM</v>
+        <v>4/20/2026, 1:12:30 PM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -745,7 +745,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDL Motor; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X7; X8; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X81; X82; X83; X84; X85; X86; X87; X88; X93; X95; X96; X97; X98; X99; X100; X101; X102; X103; X104</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDL; CDL Motor; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; LED; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X7; X8; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X81; X82; X83; X84; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; ZombieDisplay</v>
       </c>
       <c r="B9" t="str">
         <v>connector</v>
@@ -760,7 +760,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G9" t="str">
         <v>ea</v>
@@ -950,7 +950,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; F13.OUT_F21.OUT; F23.IN_X104.1; FrontDtsch12-M.6_Precharge Relay.Coil-; FrontDtsch12-M.7_HV+ Contactor.Coil-; HV- Contactor.Coil-_RearDtsch12-M.7; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
+        <v>EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; F13.OUT_F21.OUT; InDtsch12-M.5_X1.31; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
       </c>
       <c r="B14" t="str">
         <v>wire</v>
@@ -965,7 +965,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G14" t="str">
         <v>ea</v>
@@ -986,7 +986,7 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; F13.OUT_F21.OUT; F23.IN_X104.1; FrontDtsch12-M.6_Precharge Relay.Coil-; FrontDtsch12-M.7_HV+ Contactor.Coil-; HV- Contactor.Coil-_RearDtsch12-M.7; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
+        <v>EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; F13.OUT_F21.OUT; InDtsch12-M.5_X1.31; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
       </c>
     </row>
     <row r="15">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>DCDC-F.1_FrontDtsch12-M.1; DCDC-R.1_RearDtsch12-M.1; FrontDtsch12-F.1_RearDtsch12-F.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.3_X98.1; PBCtrl.6_GrnLed.2</v>
+        <v>FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_DCDC-R.1; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
       <c r="B26" t="str">
         <v>wire</v>
@@ -1457,7 +1457,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G26" t="str">
         <v>ea</v>
@@ -1478,7 +1478,7 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v>DCDC-F.1_FrontDtsch12-M.1; DCDC-R.1_RearDtsch12-M.1; FrontDtsch12-F.1_RearDtsch12-F.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.3_X98.1; PBCtrl.6_GrnLed.2</v>
+        <v>FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_DCDC-R.1; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
     </row>
     <row r="27">
@@ -1524,7 +1524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>BMS-F.4_CanLO.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; PBCtrl.7_GrnLed.1</v>
+        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1539,7 +1539,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28" t="str">
         <v>ea</v>
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>BMS-F.4_CanLO.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; PBCtrl.7_GrnLed.1</v>
+        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="29">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>DCDC-F.2_FrontDtsch12-M.12; DCDC-R.2_RearDtsch12-M.12; FrontDtsch12-F.12_RearDtsch12-F.12; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1</v>
+        <v>F17.OUT_Precharge Relay.Coil+; F17.OUT_Precharge Relay.Coil+; F17.OUT_Precharge Relay.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; RearDtsch12-M.12_DCDC-R.2</v>
       </c>
       <c r="B36" t="str">
         <v>wire</v>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G36" t="str">
         <v>ea</v>
@@ -1888,7 +1888,7 @@
         <v/>
       </c>
       <c r="M36" t="str">
-        <v>DCDC-F.2_FrontDtsch12-M.12; DCDC-R.2_RearDtsch12-M.12; FrontDtsch12-F.12_RearDtsch12-F.12; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1</v>
+        <v>F17.OUT_Precharge Relay.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; RearDtsch12-M.12_DCDC-R.2</v>
       </c>
     </row>
     <row r="37">
@@ -2221,7 +2221,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BMS-F.3_CanHI.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1</v>
+        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B45" t="str">
         <v>wire</v>
@@ -2236,7 +2236,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G45" t="str">
         <v>ea</v>
@@ -2257,7 +2257,7 @@
         <v/>
       </c>
       <c r="M45" t="str">
-        <v>BMS-F.3_CanHI.2; BMS-R.3_Term.1; BMS-R.4_Term.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1</v>
+        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="46">
@@ -2344,7 +2344,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Precharge Relay.Coil+_X95.1</v>
+        <v>F21.IN_X96.1</v>
       </c>
       <c r="B48" t="str">
         <v>wire</v>
@@ -2365,10 +2365,10 @@
         <v>ea</v>
       </c>
       <c r="H48" t="str">
-        <v>16 AWG</v>
+        <v>12 AWG</v>
       </c>
       <c r="I48" t="str">
-        <v>VT</v>
+        <v>RD</v>
       </c>
       <c r="J48" t="str">
         <v/>
@@ -2380,12 +2380,12 @@
         <v/>
       </c>
       <c r="M48" t="str">
-        <v>Precharge Relay.Coil+_X95.1</v>
+        <v>F21.IN_X96.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>F21.IN_X96.1</v>
+        <v>F22.IN_X97.1; F22.OUT_X1.56</v>
       </c>
       <c r="B49" t="str">
         <v>wire</v>
@@ -2400,13 +2400,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="str">
         <v>ea</v>
       </c>
       <c r="H49" t="str">
-        <v>12 AWG</v>
+        <v>16 AWG</v>
       </c>
       <c r="I49" t="str">
         <v>RD</v>
@@ -2421,12 +2421,12 @@
         <v/>
       </c>
       <c r="M49" t="str">
-        <v>F21.IN_X96.1</v>
+        <v>F22.IN_X97.1; F22.OUT_X1.56</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>F22.IN_X97.1; F22.OUT_X1.56</v>
+        <v>PBCtrl.1_Caliper.1</v>
       </c>
       <c r="B50" t="str">
         <v>wire</v>
@@ -2441,16 +2441,16 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" t="str">
         <v>ea</v>
       </c>
       <c r="H50" t="str">
-        <v>16 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I50" t="str">
-        <v>RD</v>
+        <v>WH</v>
       </c>
       <c r="J50" t="str">
         <v/>
@@ -2462,12 +2462,12 @@
         <v/>
       </c>
       <c r="M50" t="str">
-        <v>F22.IN_X97.1; F22.OUT_X1.56</v>
+        <v>PBCtrl.1_Caliper.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>PBCtrl.1_Caliper.1</v>
+        <v>PBCtrl.2_Caliper.2</v>
       </c>
       <c r="B51" t="str">
         <v>wire</v>
@@ -2491,7 +2491,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I51" t="str">
-        <v>WH</v>
+        <v>YE</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2503,12 +2503,12 @@
         <v/>
       </c>
       <c r="M51" t="str">
-        <v>PBCtrl.1_Caliper.1</v>
+        <v>PBCtrl.2_Caliper.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PBCtrl.2_Caliper.2</v>
+        <v>PBCtrl.3_X98.1</v>
       </c>
       <c r="B52" t="str">
         <v>wire</v>
@@ -2532,7 +2532,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I52" t="str">
-        <v>YE</v>
+        <v>BK</v>
       </c>
       <c r="J52" t="str">
         <v/>
@@ -2544,12 +2544,12 @@
         <v/>
       </c>
       <c r="M52" t="str">
-        <v>PBCtrl.2_Caliper.2</v>
+        <v>PBCtrl.3_X98.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>PBCtrl.4_F23.OUT</v>
+        <v>F14.OUT_PBCtrl.4</v>
       </c>
       <c r="B53" t="str">
         <v>wire</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="M53" t="str">
-        <v>PBCtrl.4_F23.OUT</v>
+        <v>F14.OUT_PBCtrl.4</v>
       </c>
     </row>
     <row r="54">
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G54" t="str">
         <v>ea</v>
@@ -2707,7 +2707,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>4/20/2026, 1:12:30 PM</v>
+        <v>4/21/2026, 12:48:31 PM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -1852,7 +1852,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>F17.OUT_Precharge Relay.Coil+; F17.OUT_Precharge Relay.Coil+; F17.OUT_Precharge Relay.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; RearDtsch12-M.12_DCDC-R.2</v>
+        <v>FrontDtsch12-F.12_RearDtsch12-F.12; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; Precharge Relay.Coil+_HV- Contactor.Coil+; Precharge Relay.Coil+_HV- Contactor.Coil+; Precharge Relay.Coil+_HV- Contactor.Coil+; RearDtsch12-M.12_DCDC-R.2</v>
       </c>
       <c r="B36" t="str">
         <v>wire</v>
@@ -1888,7 +1888,7 @@
         <v/>
       </c>
       <c r="M36" t="str">
-        <v>F17.OUT_Precharge Relay.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; RearDtsch12-M.12_DCDC-R.2</v>
+        <v>FrontDtsch12-F.12_RearDtsch12-F.12; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; Precharge Relay.Coil+_HV- Contactor.Coil+; RearDtsch12-M.12_DCDC-R.2</v>
       </c>
     </row>
     <row r="37">
@@ -2707,7 +2707,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>4/21/2026, 12:48:31 PM</v>
+        <v>4/21/2026, 1:23:10 PM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -745,7 +745,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDL; CDL Motor; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; LED; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X7; X8; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X81; X82; X83; X84; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; ZombieDisplay</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDL; CDL Motor; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; LED; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X81; X82; X83; X84; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; ZombieDisplay</v>
       </c>
       <c r="B9" t="str">
         <v>connector</v>
@@ -760,7 +760,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G9" t="str">
         <v>ea</v>
@@ -772,7 +772,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85; X4.30_X7.6</v>
+        <v>Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; Bat+.10_K12.30</v>
       </c>
       <c r="B21" t="str">
         <v>wire</v>
@@ -1252,16 +1252,16 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G21" t="str">
         <v>ea</v>
       </c>
       <c r="H21" t="str">
-        <v>18 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I21" t="str">
-        <v>BK</v>
+        <v>RD</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1273,12 +1273,12 @@
         <v/>
       </c>
       <c r="M21" t="str">
-        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85; X4.30_X7.6</v>
+        <v>Bat+.10_K12.30; Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; Bat+.10_K12.30; X7.5_X8</v>
+        <v>K11.87_F11.IN; K12.87_F12.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
       </c>
       <c r="B22" t="str">
         <v>wire</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22" t="str">
         <v>ea</v>
@@ -1302,7 +1302,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I22" t="str">
-        <v>RD</v>
+        <v/>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1314,12 +1314,12 @@
         <v/>
       </c>
       <c r="M22" t="str">
-        <v>Bat+.10_K12.30; Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; X7.5_X8</v>
+        <v>K11.87_F11.IN; K12.87_F12.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>K11.87_F11.IN; K12.87_F12.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
+        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
       </c>
       <c r="B23" t="str">
         <v>wire</v>
@@ -1334,16 +1334,16 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G23" t="str">
         <v>ea</v>
       </c>
       <c r="H23" t="str">
-        <v>14 AWG</v>
+        <v>18 AWG</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>VT</v>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1355,12 +1355,12 @@
         <v/>
       </c>
       <c r="M23" t="str">
-        <v>K11.87_F11.IN; K12.87_F12.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
+        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
+        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85</v>
       </c>
       <c r="B24" t="str">
         <v>wire</v>
@@ -1375,7 +1375,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G24" t="str">
         <v>ea</v>
@@ -1384,7 +1384,7 @@
         <v>18 AWG</v>
       </c>
       <c r="I24" t="str">
-        <v>VT</v>
+        <v>BK</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1396,7 +1396,7 @@
         <v/>
       </c>
       <c r="M24" t="str">
-        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
+        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85</v>
       </c>
     </row>
     <row r="25">
@@ -2707,7 +2707,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>4/21/2026, 1:23:10 PM</v>
+        <v>4/21/2026, 3:49:16 PM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -745,7 +745,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDL; CDL Motor; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; LED; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X81; X82; X83; X84; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; ZombieDisplay</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDL; CDL Motor; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; LED; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X81; X82; X83; X84; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; ZombieDisplay</v>
       </c>
       <c r="B9" t="str">
         <v>connector</v>
@@ -760,7 +760,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G9" t="str">
         <v>ea</v>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; FrontDtsch12-M.1_DCDC-F.1; Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85</v>
       </c>
       <c r="B24" t="str">
         <v>wire</v>
@@ -1375,7 +1375,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G24" t="str">
         <v>ea</v>
@@ -1396,7 +1396,7 @@
         <v/>
       </c>
       <c r="M24" t="str">
-        <v>Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85</v>
       </c>
     </row>
     <row r="25">
@@ -1483,7 +1483,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2</v>
+        <v>FrontDtsch12-F.2_RearDtsch12-F.2; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
       <c r="B27" t="str">
         <v>wire</v>
@@ -1498,7 +1498,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" t="str">
         <v>ea</v>
@@ -1519,7 +1519,7 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2</v>
+        <v>FrontDtsch12-F.2_RearDtsch12-F.2; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
     </row>
     <row r="28">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>FrontDtsch12-F.12_RearDtsch12-F.12; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; Precharge Relay.Coil+_HV- Contactor.Coil+; Precharge Relay.Coil+_HV- Contactor.Coil+; Precharge Relay.Coil+_HV- Contactor.Coil+; RearDtsch12-M.12_DCDC-R.2</v>
+        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
       <c r="B36" t="str">
         <v>wire</v>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G36" t="str">
         <v>ea</v>
@@ -1888,7 +1888,7 @@
         <v/>
       </c>
       <c r="M36" t="str">
-        <v>FrontDtsch12-F.12_RearDtsch12-F.12; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; Precharge Relay.Coil+_HV- Contactor.Coil+; RearDtsch12-M.12_DCDC-R.2</v>
+        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
     </row>
     <row r="37">
@@ -2707,7 +2707,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>4/21/2026, 3:49:16 PM</v>
+        <v>4/22/2026, 1:19:33 PM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M61"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -745,7 +745,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDL; CDL Motor; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; LED; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X81; X82; X83; X84; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; ZombieDisplay</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDLLED; CDLSw; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X81; X82; X83; X84; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; ZombieDisplay</v>
       </c>
       <c r="B9" t="str">
         <v>connector</v>
@@ -760,7 +760,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G9" t="str">
         <v>ea</v>
@@ -950,7 +950,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; F13.OUT_F21.OUT; InDtsch12-M.5_X1.31; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
+        <v>F13.OUT_F21.OUT; InDtsch12-M.5_X1.31; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
       </c>
       <c r="B14" t="str">
         <v>wire</v>
@@ -965,7 +965,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G14" t="str">
         <v>ea</v>
@@ -986,7 +986,7 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>EC1.10_CDL Motor.4; EC1.11_CDL Motor.6; EC1.12_CDL Motor.5; EC1.4_CtrlRelay.7; EC1.7_CtrlRelay.1; EC1.8_CtrlRelay.4; F13.OUT_F21.OUT; InDtsch12-M.5_X1.31; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
+        <v>F13.OUT_F21.OUT; InDtsch12-M.5_X1.31; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
       </c>
     </row>
     <row r="15">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_DCDC-R.1; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
       <c r="B26" t="str">
         <v>wire</v>
@@ -1457,7 +1457,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" t="str">
         <v>ea</v>
@@ -1478,7 +1478,7 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v>FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_DCDC-R.1; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
     </row>
     <row r="27">
@@ -1524,7 +1524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.3_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.3_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="29">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.5; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
       <c r="B36" t="str">
         <v>wire</v>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G36" t="str">
         <v>ea</v>
@@ -1888,7 +1888,7 @@
         <v/>
       </c>
       <c r="M36" t="str">
-        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.5; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>20 AWG</v>
       </c>
       <c r="I38" t="str">
-        <v>RD</v>
+        <v>OG</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.2_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B45" t="str">
         <v>wire</v>
@@ -2257,7 +2257,7 @@
         <v/>
       </c>
       <c r="M45" t="str">
-        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.2_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="46">
@@ -2549,7 +2549,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>F14.OUT_PBCtrl.4</v>
+        <v>CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1</v>
       </c>
       <c r="B53" t="str">
         <v>wire</v>
@@ -2564,7 +2564,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G53" t="str">
         <v>ea</v>
@@ -2585,53 +2585,340 @@
         <v/>
       </c>
       <c r="M53" t="str">
-        <v>F14.OUT_PBCtrl.4</v>
+        <v>CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
+        <v>RearDtsch12-M.1_PWR.Gnd</v>
+      </c>
+      <c r="B54" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>1</v>
+      </c>
+      <c r="G54" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H54" t="str">
+        <v>20 AWG</v>
+      </c>
+      <c r="I54" t="str">
+        <v>BK</v>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v>RearDtsch12-M.1_PWR.Gnd</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>CtrlRelay.4_EC1.2</v>
+      </c>
+      <c r="B55" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>1</v>
+      </c>
+      <c r="G55" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H55" t="str">
+        <v>14 AWG</v>
+      </c>
+      <c r="I55" t="str">
+        <v>GNBU</v>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v>CtrlRelay.4_EC1.2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>CtrlRelay.10_EC1.5</v>
+      </c>
+      <c r="B56" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>1</v>
+      </c>
+      <c r="G56" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H56" t="str">
+        <v>16 AWG</v>
+      </c>
+      <c r="I56" t="str">
+        <v>GNBK</v>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v>CtrlRelay.10_EC1.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>CtrlRelay.1_EC1.3</v>
+      </c>
+      <c r="B57" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>1</v>
+      </c>
+      <c r="G57" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H57" t="str">
+        <v>14 AWG</v>
+      </c>
+      <c r="I57" t="str">
+        <v>GN</v>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v>CtrlRelay.1_EC1.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>CtrlRelay.5_EC1.6</v>
+      </c>
+      <c r="B58" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>1</v>
+      </c>
+      <c r="G58" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H58" t="str">
+        <v>16 AWG</v>
+      </c>
+      <c r="I58" t="str">
+        <v>GNYE</v>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v>CtrlRelay.5_EC1.6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>EC1.4_CDLLED.2</v>
+      </c>
+      <c r="B59" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>1</v>
+      </c>
+      <c r="G59" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v>WHBK</v>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v>EC1.4_CDLLED.2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>CDLSw.1_CtrlRelay.7</v>
+      </c>
+      <c r="B60" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>1</v>
+      </c>
+      <c r="G60" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v>BKRD</v>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v>CDLSw.1_CtrlRelay.7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
         <v>10863985</v>
       </c>
-      <c r="B54" t="str">
+      <c r="B61" t="str">
         <v>contact</v>
       </c>
-      <c r="C54" t="str">
+      <c r="C61" t="str">
         <v>10863985</v>
       </c>
-      <c r="D54" t="str">
+      <c r="D61" t="str">
         <v>Aptiv</v>
       </c>
-      <c r="E54" t="str">
-        <v/>
-      </c>
-      <c r="F54" t="str">
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
         <v>40</v>
       </c>
-      <c r="G54" t="str">
-        <v>ea</v>
-      </c>
-      <c r="H54" t="str">
-        <v/>
-      </c>
-      <c r="I54" t="str">
-        <v/>
-      </c>
-      <c r="J54" t="str">
-        <v/>
-      </c>
-      <c r="K54" t="str">
-        <v/>
-      </c>
-      <c r="L54" t="str">
-        <v/>
-      </c>
-      <c r="M54" t="str">
+      <c r="G61" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2691,7 +2978,7 @@
         <v>Total Wires</v>
       </c>
       <c r="B9">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -2707,7 +2994,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>4/22/2026, 1:19:33 PM</v>
+        <v>4/23/2026, 1:11:25 PM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -745,7 +745,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDLLED; CDLSw; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X81; X82; X83; X84; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; ZombieDisplay</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDLLED; CDLSw; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; X106; X107; X108; ZombieDisplay</v>
       </c>
       <c r="B9" t="str">
         <v>connector</v>
@@ -760,7 +760,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G9" t="str">
         <v>ea</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
       <c r="B27" t="str">
         <v>wire</v>
@@ -1498,7 +1498,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" t="str">
         <v>ea</v>
@@ -1519,12 +1519,12 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.3_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.3_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="29">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.5; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
       <c r="B36" t="str">
         <v>wire</v>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G36" t="str">
         <v>ea</v>
@@ -1888,12 +1888,12 @@
         <v/>
       </c>
       <c r="M36" t="str">
-        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.5; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
+        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
       </c>
       <c r="B37" t="str">
         <v>wire</v>
@@ -1908,7 +1908,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" t="str">
         <v>ea</v>
@@ -1929,7 +1929,7 @@
         <v/>
       </c>
       <c r="M37" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
+        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
       </c>
     </row>
     <row r="38">
@@ -2057,7 +2057,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HV Bat Front.V-_X84.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Neg Fuse.OUT_X85.1</v>
+        <v>HV DiscFrontF.+_X108.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
       <c r="B41" t="str">
         <v>wire</v>
@@ -2072,13 +2072,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G41" t="str">
         <v>ea</v>
       </c>
       <c r="H41" t="str">
-        <v>3/0 AWG</v>
+        <v/>
       </c>
       <c r="I41" t="str">
         <v>OGBK</v>
@@ -2093,12 +2093,12 @@
         <v/>
       </c>
       <c r="M41" t="str">
-        <v>HV Bat Front.V-_X84.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Neg Fuse.OUT_X85.1</v>
+        <v>HV DiscFrontF.+_X108.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Neg Fuse.OUT_X85.1</v>
+        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
       <c r="B42" t="str">
         <v>wire</v>
@@ -2113,13 +2113,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G42" t="str">
         <v>ea</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>3/0 AWG</v>
       </c>
       <c r="I42" t="str">
         <v>OGBK</v>
@@ -2134,7 +2134,7 @@
         <v/>
       </c>
       <c r="M42" t="str">
-        <v>Neg Fuse.OUT_X85.1</v>
+        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
     </row>
     <row r="43">
@@ -2221,7 +2221,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.2_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B45" t="str">
         <v>wire</v>
@@ -2257,7 +2257,7 @@
         <v/>
       </c>
       <c r="M45" t="str">
-        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.2_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="46">
@@ -2877,48 +2877,89 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
+        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
+      </c>
+      <c r="B61" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>1</v>
+      </c>
+      <c r="G61" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v>OGRD</v>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
         <v>10863985</v>
       </c>
-      <c r="B61" t="str">
+      <c r="B62" t="str">
         <v>contact</v>
       </c>
-      <c r="C61" t="str">
+      <c r="C62" t="str">
         <v>10863985</v>
       </c>
-      <c r="D61" t="str">
+      <c r="D62" t="str">
         <v>Aptiv</v>
       </c>
-      <c r="E61" t="str">
-        <v/>
-      </c>
-      <c r="F61" t="str">
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
         <v>40</v>
       </c>
-      <c r="G61" t="str">
-        <v>ea</v>
-      </c>
-      <c r="H61" t="str">
-        <v/>
-      </c>
-      <c r="I61" t="str">
-        <v/>
-      </c>
-      <c r="J61" t="str">
-        <v/>
-      </c>
-      <c r="K61" t="str">
-        <v/>
-      </c>
-      <c r="L61" t="str">
-        <v/>
-      </c>
-      <c r="M61" t="str">
+      <c r="G62" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M62"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2978,7 +3019,7 @@
         <v>Total Wires</v>
       </c>
       <c r="B9">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -2994,7 +3035,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>4/23/2026, 1:11:25 PM</v>
+        <v>4/28/2026, 1:51:28 PM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -745,7 +745,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN1; CAN2; CanHI; CanLO; CDLLED; CDLSw; Chassis; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; SENSE; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; X106; X107; X108; ZombieDisplay</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; DashDisplay; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; X106; X107; X108; X109; ZombieDisplay</v>
       </c>
       <c r="B9" t="str">
         <v>connector</v>
@@ -760,7 +760,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G9" t="str">
         <v>ea</v>
@@ -950,7 +950,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>F13.OUT_F21.OUT; InDtsch12-M.5_X1.31; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
+        <v>InDtsch12-M.5_X1.4; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
       </c>
       <c r="B14" t="str">
         <v>wire</v>
@@ -965,7 +965,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14" t="str">
         <v>ea</v>
@@ -986,7 +986,7 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>F13.OUT_F21.OUT; InDtsch12-M.5_X1.31; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
+        <v>InDtsch12-M.5_X1.4; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
       </c>
     </row>
     <row r="15">
@@ -1483,7 +1483,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
       <c r="B27" t="str">
         <v>wire</v>
@@ -1498,7 +1498,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G27" t="str">
         <v>ea</v>
@@ -1519,12 +1519,12 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1539,7 +1539,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G28" t="str">
         <v>ea</v>
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>BMS-F.4_CanLO.2; CAN1.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="29">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>NET_mnnbwso0_7</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
       </c>
       <c r="B38" t="str">
         <v>wire</v>
@@ -1949,7 +1949,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" t="str">
         <v>ea</v>
@@ -1970,7 +1970,7 @@
         <v/>
       </c>
       <c r="M38" t="str">
-        <v>NET_mnnbwso0_7</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
       </c>
     </row>
     <row r="39">
@@ -2221,7 +2221,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B45" t="str">
         <v>wire</v>
@@ -2257,7 +2257,7 @@
         <v/>
       </c>
       <c r="M45" t="str">
-        <v>BMS-F.3_CanHI.2; CAN1.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="46">
@@ -2303,7 +2303,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>F13.OUT_F21.OUT</v>
+        <v>F13.OUT_OilPump.5</v>
       </c>
       <c r="B47" t="str">
         <v>wire</v>
@@ -2339,7 +2339,7 @@
         <v/>
       </c>
       <c r="M47" t="str">
-        <v>F13.OUT_F21.OUT</v>
+        <v>F13.OUT_OilPump.5</v>
       </c>
     </row>
     <row r="48">
@@ -2933,7 +2933,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G62" t="str">
         <v>ea</v>
@@ -3035,7 +3035,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>4/28/2026, 1:51:28 PM</v>
+        <v>5/17/2026, 3:41:33 PM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -458,16 +458,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CtrlRelay</v>
+        <v>MitsuCtrl</v>
       </c>
       <c r="B2" t="str">
         <v>connector</v>
       </c>
       <c r="C2" t="str">
-        <v>89531-60010</v>
+        <v>6189-1092 13-WAY CONNECTOR KIT Inc Terminals &amp; seals [13-AC001</v>
       </c>
       <c r="D2" t="str">
-        <v>Toyota</v>
+        <v>Sumitomo</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -485,7 +485,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -499,16 +499,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>X3</v>
+        <v>CtrlRelay</v>
       </c>
       <c r="B3" t="str">
         <v>connector</v>
       </c>
       <c r="C3" t="str">
-        <v>90980-12326</v>
+        <v>89531-60010</v>
       </c>
       <c r="D3" t="str">
-        <v>Sumitomo</v>
+        <v>Toyota</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -540,13 +540,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>X5; X6</v>
+        <v>X3</v>
       </c>
       <c r="B4" t="str">
         <v>connector</v>
       </c>
       <c r="C4" t="str">
-        <v>90980-12520</v>
+        <v>90980-12326</v>
       </c>
       <c r="D4" t="str">
         <v>Sumitomo</v>
@@ -555,7 +555,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="str">
         <v>ea</v>
@@ -567,7 +567,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -581,22 +581,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>X1</v>
+        <v>X5; X6</v>
       </c>
       <c r="B5" t="str">
         <v>connector</v>
       </c>
       <c r="C5" t="str">
-        <v>13669859</v>
+        <v>90980-12520</v>
       </c>
       <c r="D5" t="str">
-        <v>Aptiv</v>
+        <v>Sumitomo</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="str">
         <v>ea</v>
@@ -608,7 +608,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -622,13 +622,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>J1</v>
+        <v>X1</v>
       </c>
       <c r="B6" t="str">
         <v>connector</v>
       </c>
       <c r="C6" t="str">
-        <v>33511394</v>
+        <v>13669859</v>
       </c>
       <c r="D6" t="str">
         <v>Aptiv</v>
@@ -663,16 +663,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>X2</v>
+        <v>J1</v>
       </c>
       <c r="B7" t="str">
         <v>connector</v>
       </c>
       <c r="C7" t="str">
-        <v>HX040-6P</v>
+        <v>33511394</v>
       </c>
       <c r="D7" t="str">
-        <v>Sumitomo</v>
+        <v>Aptiv</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -690,7 +690,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -704,16 +704,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>X4</v>
+        <v>X2</v>
       </c>
       <c r="B8" t="str">
         <v>connector</v>
       </c>
       <c r="C8" t="str">
-        <v>LS600HL</v>
+        <v>HX040-6P</v>
       </c>
       <c r="D8" t="str">
-        <v>Lexus</v>
+        <v>Sumitomo</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -731,7 +731,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -745,22 +745,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; DashDisplay; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X60; X61; X62; X63; X64; X65; X66; X67; X68; X69; X70; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; X106; X107; X108; X109; ZombieDisplay</v>
+        <v>X4</v>
       </c>
       <c r="B9" t="str">
         <v>connector</v>
       </c>
       <c r="C9" t="str">
-        <v>Unassigned</v>
+        <v>LS600HL</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>Lexus</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="G9" t="str">
         <v>ea</v>
@@ -772,7 +772,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -786,10 +786,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>X2.1_X1.45</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; DashDisplay; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X61; X62; X63; X64; X65; X67; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; X106; X107; X108; X109; X110; X111; X112; X113; ZombieDisplay</v>
       </c>
       <c r="B10" t="str">
-        <v>wire</v>
+        <v>connector</v>
       </c>
       <c r="C10" t="str">
         <v>Unassigned</v>
@@ -801,19 +801,19 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="G10" t="str">
         <v>ea</v>
       </c>
       <c r="H10" t="str">
-        <v>20 AWG</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>YEBU</v>
+        <v/>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>14</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -822,12 +822,12 @@
         <v/>
       </c>
       <c r="M10" t="str">
-        <v>X2.1_X1.45</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>J1.46_X2.2</v>
+        <v>X2.1_X1.45</v>
       </c>
       <c r="B11" t="str">
         <v>wire</v>
@@ -851,7 +851,7 @@
         <v>20 AWG</v>
       </c>
       <c r="I11" t="str">
-        <v>BNBU</v>
+        <v>YEBU</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -863,12 +863,12 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>J1.46_X2.2</v>
+        <v>X2.1_X1.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>X2.5_X1.47</v>
+        <v>J1.46_X2.2</v>
       </c>
       <c r="B12" t="str">
         <v>wire</v>
@@ -892,7 +892,7 @@
         <v>20 AWG</v>
       </c>
       <c r="I12" t="str">
-        <v>WHBU</v>
+        <v>BNBU</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -904,12 +904,12 @@
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>X2.5_X1.47</v>
+        <v>J1.46_X2.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>J1.48_X2.3</v>
+        <v>X2.5_X1.47</v>
       </c>
       <c r="B13" t="str">
         <v>wire</v>
@@ -933,7 +933,7 @@
         <v>20 AWG</v>
       </c>
       <c r="I13" t="str">
-        <v>WHGN</v>
+        <v>WHBU</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -945,12 +945,12 @@
         <v/>
       </c>
       <c r="M13" t="str">
-        <v>J1.48_X2.3</v>
+        <v>X2.5_X1.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>InDtsch12-M.5_X1.4; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
+        <v>J1.48_X2.3</v>
       </c>
       <c r="B14" t="str">
         <v>wire</v>
@@ -965,16 +965,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G14" t="str">
         <v>ea</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>20 AWG</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>WHGN</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -986,12 +986,12 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>InDtsch12-M.5_X1.4; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
+        <v>J1.48_X2.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>J1.16_X4.34; J1.18_X4.13; J1.20_X4.2; J1.22_X4.22; X4.17_X5.3; X6.3_X4.38</v>
+        <v>InDtsch12-M.5_K12.86; InDtsch12-M.5_K12.86; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
       </c>
       <c r="B15" t="str">
         <v>wire</v>
@@ -1006,16 +1006,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G15" t="str">
         <v>ea</v>
       </c>
       <c r="H15" t="str">
-        <v>22 AWG</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>WH</v>
+        <v/>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -1027,12 +1027,12 @@
         <v/>
       </c>
       <c r="M15" t="str">
-        <v>J1.16_X4.34; J1.18_X4.13; J1.20_X4.2; J1.22_X4.22; X4.17_X5.3; X6.3_X4.38</v>
+        <v>InDtsch12-M.5_K12.86; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>J1.17_X4.35; J1.19_X4.14; J1.21_X4.3; J1.23_X4.23; X4.20_X5.1; X6.1_X4.40</v>
+        <v>J1.16_X4.34; J1.18_X4.13; J1.20_X4.2; J1.22_X4.22; X4.17_X5.3; X6.3_X4.38</v>
       </c>
       <c r="B16" t="str">
         <v>wire</v>
@@ -1056,7 +1056,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I16" t="str">
-        <v>BK</v>
+        <v>WH</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1068,12 +1068,12 @@
         <v/>
       </c>
       <c r="M16" t="str">
-        <v>J1.17_X4.35; J1.19_X4.14; J1.21_X4.3; J1.23_X4.23; X4.20_X5.1; X6.1_X4.40</v>
+        <v>J1.16_X4.34; J1.18_X4.13; J1.20_X4.2; J1.22_X4.22; X4.17_X5.3; X6.3_X4.38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>X4.18_X5.2; X6.2_X4.39</v>
+        <v>J1.17_X4.35; J1.19_X4.14; J1.21_X4.3; J1.23_X4.23; X4.20_X5.1; X6.1_X4.40</v>
       </c>
       <c r="B17" t="str">
         <v>wire</v>
@@ -1088,7 +1088,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G17" t="str">
         <v>ea</v>
@@ -1097,7 +1097,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I17" t="str">
-        <v>BU</v>
+        <v>BK</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1109,12 +1109,12 @@
         <v/>
       </c>
       <c r="M17" t="str">
-        <v>X4.18_X5.2; X6.2_X4.39</v>
+        <v>J1.17_X4.35; J1.19_X4.14; J1.21_X4.3; J1.23_X4.23; X4.20_X5.1; X6.1_X4.40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>X4.9_X5.5; X6.5_X4.27</v>
+        <v>X4.18_X5.2; X6.2_X4.39</v>
       </c>
       <c r="B18" t="str">
         <v>wire</v>
@@ -1138,7 +1138,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I18" t="str">
-        <v>GN</v>
+        <v>BU</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1150,12 +1150,12 @@
         <v/>
       </c>
       <c r="M18" t="str">
-        <v>X4.9_X5.5; X6.5_X4.27</v>
+        <v>X4.18_X5.2; X6.2_X4.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>X4.7_X5.6; X6.6_X4.29</v>
+        <v>X4.9_X5.5; X6.5_X4.27</v>
       </c>
       <c r="B19" t="str">
         <v>wire</v>
@@ -1179,7 +1179,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I19" t="str">
-        <v>RD</v>
+        <v>GN</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1191,12 +1191,12 @@
         <v/>
       </c>
       <c r="M19" t="str">
-        <v>X4.7_X5.6; X6.6_X4.29</v>
+        <v>X4.9_X5.5; X6.5_X4.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>X4.6_X5.7; X6.7_X4.28</v>
+        <v>X4.7_X5.6; X6.6_X4.29</v>
       </c>
       <c r="B20" t="str">
         <v>wire</v>
@@ -1220,7 +1220,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I20" t="str">
-        <v>YE</v>
+        <v>RD</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1232,12 +1232,12 @@
         <v/>
       </c>
       <c r="M20" t="str">
-        <v>X4.6_X5.7; X6.7_X4.28</v>
+        <v>X4.7_X5.6; X6.6_X4.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; Bat+.10_K12.30</v>
+        <v>X4.6_X5.7; X6.7_X4.28</v>
       </c>
       <c r="B21" t="str">
         <v>wire</v>
@@ -1252,16 +1252,16 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G21" t="str">
         <v>ea</v>
       </c>
       <c r="H21" t="str">
-        <v>14 AWG</v>
+        <v>22 AWG</v>
       </c>
       <c r="I21" t="str">
-        <v>RD</v>
+        <v>YE</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1273,12 +1273,12 @@
         <v/>
       </c>
       <c r="M21" t="str">
-        <v>Bat+.10_K12.30; Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30</v>
+        <v>X4.6_X5.7; X6.7_X4.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>K11.87_F11.IN; K12.87_F12.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
+        <v>Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; Bat+.10_K12.30; K12.87_F12.IN</v>
       </c>
       <c r="B22" t="str">
         <v>wire</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" t="str">
         <v>ea</v>
@@ -1302,7 +1302,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>RD</v>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1314,12 +1314,12 @@
         <v/>
       </c>
       <c r="M22" t="str">
-        <v>K11.87_F11.IN; K12.87_F12.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
+        <v>Bat+.10_K12.30; Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; K12.87_F12.IN</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
+        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
       </c>
       <c r="B23" t="str">
         <v>wire</v>
@@ -1334,16 +1334,16 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G23" t="str">
         <v>ea</v>
       </c>
       <c r="H23" t="str">
-        <v>18 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I23" t="str">
-        <v>VT</v>
+        <v/>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1355,12 +1355,12 @@
         <v/>
       </c>
       <c r="M23" t="str">
-        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
+        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FrontDtsch12-M.1_DCDC-F.1; FrontDtsch12-M.1_DCDC-F.1; Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85</v>
+        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
       </c>
       <c r="B24" t="str">
         <v>wire</v>
@@ -1375,7 +1375,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G24" t="str">
         <v>ea</v>
@@ -1384,7 +1384,7 @@
         <v>18 AWG</v>
       </c>
       <c r="I24" t="str">
-        <v>BK</v>
+        <v>VT</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1396,12 +1396,12 @@
         <v/>
       </c>
       <c r="M24" t="str">
-        <v>FrontDtsch12-M.1_DCDC-F.1; Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.1_K17.85; GndCtrl.2_K18.85</v>
+        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86; BatCtrl.5_K12.86</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; FrontDtsch12-M.1_DCDC-F.1; Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.2_K18.85</v>
       </c>
       <c r="B25" t="str">
         <v>wire</v>
@@ -1416,7 +1416,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G25" t="str">
         <v>ea</v>
@@ -1425,7 +1425,7 @@
         <v>18 AWG</v>
       </c>
       <c r="I25" t="str">
-        <v>RD</v>
+        <v>BK</v>
       </c>
       <c r="J25" t="str">
         <v/>
@@ -1437,12 +1437,12 @@
         <v/>
       </c>
       <c r="M25" t="str">
-        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86; BatCtrl.5_K12.86</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.2_K18.85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86</v>
       </c>
       <c r="B26" t="str">
         <v>wire</v>
@@ -1457,16 +1457,16 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G26" t="str">
         <v>ea</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>18 AWG</v>
       </c>
       <c r="I26" t="str">
-        <v>BK</v>
+        <v>RD</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -1478,12 +1478,12 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X103.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K19.85_X101.1; K20.85_X102.1; MitsuCtrl.10_X111.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
       <c r="B27" t="str">
         <v>wire</v>
@@ -1498,7 +1498,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G27" t="str">
         <v>ea</v>
@@ -1507,7 +1507,7 @@
         <v/>
       </c>
       <c r="I27" t="str">
-        <v>WH</v>
+        <v>BK</v>
       </c>
       <c r="J27" t="str">
         <v/>
@@ -1519,12 +1519,12 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K19.85_X101.1; K20.85_X102.1; MitsuCtrl.10_X111.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; OilPump.5_F18.OUT; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1539,7 +1539,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G28" t="str">
         <v>ea</v>
@@ -1548,7 +1548,7 @@
         <v/>
       </c>
       <c r="I28" t="str">
-        <v>GN</v>
+        <v>WH</v>
       </c>
       <c r="J28" t="str">
         <v/>
@@ -1560,12 +1560,12 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; OilPump.5_F18.OUT; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
+        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B29" t="str">
         <v>wire</v>
@@ -1580,7 +1580,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G29" t="str">
         <v>ea</v>
@@ -1589,7 +1589,7 @@
         <v/>
       </c>
       <c r="I29" t="str">
-        <v>WHBU</v>
+        <v>GN</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -1601,12 +1601,12 @@
         <v/>
       </c>
       <c r="M29" t="str">
-        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
+        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>FrontDtsch12-F.5_RearDtsch12-F.5</v>
+        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
       </c>
       <c r="B30" t="str">
         <v>wire</v>
@@ -1630,7 +1630,7 @@
         <v/>
       </c>
       <c r="I30" t="str">
-        <v>BU</v>
+        <v>WHBU</v>
       </c>
       <c r="J30" t="str">
         <v/>
@@ -1642,12 +1642,12 @@
         <v/>
       </c>
       <c r="M30" t="str">
-        <v>FrontDtsch12-F.5_RearDtsch12-F.5</v>
+        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
+        <v>FrontDtsch12-F.5_RearDtsch12-F.5</v>
       </c>
       <c r="B31" t="str">
         <v>wire</v>
@@ -1671,7 +1671,7 @@
         <v/>
       </c>
       <c r="I31" t="str">
-        <v>WHBN</v>
+        <v>BU</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1683,12 +1683,12 @@
         <v/>
       </c>
       <c r="M31" t="str">
-        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
+        <v>FrontDtsch12-F.5_RearDtsch12-F.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_PkBrk.1</v>
+        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
       </c>
       <c r="B32" t="str">
         <v>wire</v>
@@ -1703,7 +1703,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="str">
         <v>ea</v>
@@ -1712,7 +1712,7 @@
         <v/>
       </c>
       <c r="I32" t="str">
-        <v>BN</v>
+        <v>WHBN</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1724,12 +1724,12 @@
         <v/>
       </c>
       <c r="M32" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_PkBrk.1</v>
+        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>FrontDtsch12-F.8_RearDtsch12-F.8</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_PkBrk.1</v>
       </c>
       <c r="B33" t="str">
         <v>wire</v>
@@ -1744,7 +1744,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="str">
         <v>ea</v>
@@ -1753,7 +1753,7 @@
         <v/>
       </c>
       <c r="I33" t="str">
-        <v>OG</v>
+        <v>BN</v>
       </c>
       <c r="J33" t="str">
         <v/>
@@ -1765,12 +1765,12 @@
         <v/>
       </c>
       <c r="M33" t="str">
-        <v>FrontDtsch12-F.8_RearDtsch12-F.8</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_PkBrk.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
+        <v>FrontDtsch12-F.8_RearDtsch12-F.8</v>
       </c>
       <c r="B34" t="str">
         <v>wire</v>
@@ -1794,7 +1794,7 @@
         <v/>
       </c>
       <c r="I34" t="str">
-        <v>WHOG</v>
+        <v>OG</v>
       </c>
       <c r="J34" t="str">
         <v/>
@@ -1806,12 +1806,12 @@
         <v/>
       </c>
       <c r="M34" t="str">
-        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
+        <v>FrontDtsch12-F.8_RearDtsch12-F.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
+        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
       </c>
       <c r="B35" t="str">
         <v>wire</v>
@@ -1835,7 +1835,7 @@
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>WHGN</v>
+        <v>WHOG</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -1847,12 +1847,12 @@
         <v/>
       </c>
       <c r="M35" t="str">
-        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
+        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
       </c>
       <c r="B36" t="str">
         <v>wire</v>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G36" t="str">
         <v>ea</v>
@@ -1876,7 +1876,7 @@
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>RD</v>
+        <v>WHGN</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -1888,12 +1888,12 @@
         <v/>
       </c>
       <c r="M36" t="str">
-        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K17.86_X99.1; K18.86_X100.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
+        <v>F12.OUT_MitsuCtrl.8; F21.IN_X113.1; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
       <c r="B37" t="str">
         <v>wire</v>
@@ -1908,16 +1908,16 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G37" t="str">
         <v>ea</v>
       </c>
       <c r="H37" t="str">
-        <v>3/0 AWG</v>
+        <v/>
       </c>
       <c r="I37" t="str">
-        <v>OGRD</v>
+        <v>RD</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -1929,12 +1929,12 @@
         <v/>
       </c>
       <c r="M37" t="str">
-        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
+        <v>F12.OUT_MitsuCtrl.8; F21.IN_X113.1; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
+        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
       </c>
       <c r="B38" t="str">
         <v>wire</v>
@@ -1949,16 +1949,16 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38" t="str">
         <v>ea</v>
       </c>
       <c r="H38" t="str">
-        <v>20 AWG</v>
+        <v>3/0 AWG</v>
       </c>
       <c r="I38" t="str">
-        <v>OG</v>
+        <v>OGRD</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -1970,12 +1970,12 @@
         <v/>
       </c>
       <c r="M38" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
+        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>NET_mnnb3cvb_4</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
       </c>
       <c r="B39" t="str">
         <v>wire</v>
@@ -1990,16 +1990,16 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" t="str">
         <v>ea</v>
       </c>
       <c r="H39" t="str">
-        <v>14 AWG</v>
+        <v>20 AWG</v>
       </c>
       <c r="I39" t="str">
-        <v>OGRD</v>
+        <v>OG</v>
       </c>
       <c r="J39" t="str">
         <v/>
@@ -2011,12 +2011,12 @@
         <v/>
       </c>
       <c r="M39" t="str">
-        <v>NET_mnnb3cvb_4</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
+        <v>NET_mnnb3cvb_4</v>
       </c>
       <c r="B40" t="str">
         <v>wire</v>
@@ -2031,13 +2031,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="str">
         <v>ea</v>
       </c>
       <c r="H40" t="str">
-        <v>16 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I40" t="str">
         <v>OGRD</v>
@@ -2052,12 +2052,12 @@
         <v/>
       </c>
       <c r="M40" t="str">
-        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
+        <v>NET_mnnb3cvb_4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HV DiscFrontF.+_X108.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
       </c>
       <c r="B41" t="str">
         <v>wire</v>
@@ -2072,16 +2072,16 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" t="str">
         <v>ea</v>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>16 AWG</v>
       </c>
       <c r="I41" t="str">
-        <v>OGBK</v>
+        <v>OGRD</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -2093,12 +2093,12 @@
         <v/>
       </c>
       <c r="M41" t="str">
-        <v>HV DiscFrontF.+_X108.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>HV DiscFrontF.+_X108.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
       <c r="B42" t="str">
         <v>wire</v>
@@ -2113,13 +2113,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" t="str">
         <v>ea</v>
       </c>
       <c r="H42" t="str">
-        <v>3/0 AWG</v>
+        <v/>
       </c>
       <c r="I42" t="str">
         <v>OGBK</v>
@@ -2134,12 +2134,12 @@
         <v/>
       </c>
       <c r="M42" t="str">
-        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>HV DiscFrontF.+_X108.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
+        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
       <c r="B43" t="str">
         <v>wire</v>
@@ -2154,16 +2154,16 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G43" t="str">
         <v>ea</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>3/0 AWG</v>
       </c>
       <c r="I43" t="str">
-        <v>WHRD</v>
+        <v>OGBK</v>
       </c>
       <c r="J43" t="str">
         <v/>
@@ -2175,12 +2175,12 @@
         <v/>
       </c>
       <c r="M43" t="str">
-        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
+        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
+        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
       </c>
       <c r="B44" t="str">
         <v>wire</v>
@@ -2204,7 +2204,7 @@
         <v/>
       </c>
       <c r="I44" t="str">
-        <v>RDWH</v>
+        <v>WHRD</v>
       </c>
       <c r="J44" t="str">
         <v/>
@@ -2216,12 +2216,12 @@
         <v/>
       </c>
       <c r="M44" t="str">
-        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
+        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
       </c>
       <c r="B45" t="str">
         <v>wire</v>
@@ -2236,7 +2236,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G45" t="str">
         <v>ea</v>
@@ -2245,7 +2245,7 @@
         <v/>
       </c>
       <c r="I45" t="str">
-        <v>YE</v>
+        <v>RDWH</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -2257,12 +2257,12 @@
         <v/>
       </c>
       <c r="M45" t="str">
-        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
+        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B46" t="str">
         <v>wire</v>
@@ -2277,16 +2277,16 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G46" t="str">
         <v>ea</v>
       </c>
       <c r="H46" t="str">
-        <v>12 AWG</v>
+        <v/>
       </c>
       <c r="I46" t="str">
-        <v>BK</v>
+        <v>YE</v>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -2298,12 +2298,12 @@
         <v/>
       </c>
       <c r="M46" t="str">
-        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
+        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>F13.OUT_OilPump.5</v>
+        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
       </c>
       <c r="B47" t="str">
         <v>wire</v>
@@ -2318,7 +2318,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="str">
         <v>ea</v>
@@ -2327,7 +2327,7 @@
         <v>12 AWG</v>
       </c>
       <c r="I47" t="str">
-        <v>BU</v>
+        <v>BK</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -2339,12 +2339,12 @@
         <v/>
       </c>
       <c r="M47" t="str">
-        <v>F13.OUT_OilPump.5</v>
+        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>F21.IN_X96.1</v>
+        <v>F21.IN_X113.1</v>
       </c>
       <c r="B48" t="str">
         <v>wire</v>
@@ -2380,7 +2380,7 @@
         <v/>
       </c>
       <c r="M48" t="str">
-        <v>F21.IN_X96.1</v>
+        <v>F21.IN_X113.1</v>
       </c>
     </row>
     <row r="49">
@@ -2549,7 +2549,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1</v>
+        <v>CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1; K17.86_X110.1</v>
       </c>
       <c r="B53" t="str">
         <v>wire</v>
@@ -2564,7 +2564,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G53" t="str">
         <v>ea</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="M53" t="str">
-        <v>CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1</v>
+        <v>CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1; K17.86_X110.1</v>
       </c>
     </row>
     <row r="54">
@@ -3011,7 +3011,7 @@
         <v>Total Connectors</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -3019,7 +3019,7 @@
         <v>Total Wires</v>
       </c>
       <c r="B9">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -3035,7 +3035,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>5/17/2026, 3:41:33 PM</v>
+        <v>6/2/2026, 11:56:21 AM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M60"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -786,7 +786,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; DashDisplay; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F22; F23; F24; F25; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X61; X62; X63; X64; X65; X67; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; X106; X107; X108; X109; X110; X111; X112; X113; ZombieDisplay</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; DashDisplay; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F23; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X61; X62; X63; X64; X65; X67; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; X106; X107; X108; X109; X110; X111; X112; X113; ZombieDisplay</v>
       </c>
       <c r="B10" t="str">
         <v>connector</v>
@@ -801,7 +801,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G10" t="str">
         <v>ea</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; OilPump.5_F18.OUT; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>F13.OUT_OilPump.5; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; OilPump.5_F18.OUT; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>F13.OUT_OilPump.5; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
     </row>
     <row r="29">
@@ -1893,7 +1893,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>F12.OUT_MitsuCtrl.8; F21.IN_X113.1; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>F12.OUT_MitsuCtrl.8; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K12.85_X113.1; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
       <c r="B37" t="str">
         <v>wire</v>
@@ -1929,7 +1929,7 @@
         <v/>
       </c>
       <c r="M37" t="str">
-        <v>F12.OUT_MitsuCtrl.8; F21.IN_X113.1; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>F12.OUT_MitsuCtrl.8; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K12.85_X113.1; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
     </row>
     <row r="38">
@@ -2344,7 +2344,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>F21.IN_X113.1</v>
+        <v>PBCtrl.1_Caliper.1</v>
       </c>
       <c r="B48" t="str">
         <v>wire</v>
@@ -2365,10 +2365,10 @@
         <v>ea</v>
       </c>
       <c r="H48" t="str">
-        <v>12 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I48" t="str">
-        <v>RD</v>
+        <v>WH</v>
       </c>
       <c r="J48" t="str">
         <v/>
@@ -2380,12 +2380,12 @@
         <v/>
       </c>
       <c r="M48" t="str">
-        <v>F21.IN_X113.1</v>
+        <v>PBCtrl.1_Caliper.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>F22.IN_X97.1; F22.OUT_X1.56</v>
+        <v>PBCtrl.2_Caliper.2</v>
       </c>
       <c r="B49" t="str">
         <v>wire</v>
@@ -2400,16 +2400,16 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" t="str">
         <v>ea</v>
       </c>
       <c r="H49" t="str">
-        <v>16 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I49" t="str">
-        <v>RD</v>
+        <v>YE</v>
       </c>
       <c r="J49" t="str">
         <v/>
@@ -2421,12 +2421,12 @@
         <v/>
       </c>
       <c r="M49" t="str">
-        <v>F22.IN_X97.1; F22.OUT_X1.56</v>
+        <v>PBCtrl.2_Caliper.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>PBCtrl.1_Caliper.1</v>
+        <v>PBCtrl.3_X98.1</v>
       </c>
       <c r="B50" t="str">
         <v>wire</v>
@@ -2450,7 +2450,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I50" t="str">
-        <v>WH</v>
+        <v>BK</v>
       </c>
       <c r="J50" t="str">
         <v/>
@@ -2462,12 +2462,12 @@
         <v/>
       </c>
       <c r="M50" t="str">
-        <v>PBCtrl.1_Caliper.1</v>
+        <v>PBCtrl.3_X98.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>PBCtrl.2_Caliper.2</v>
+        <v>CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1; K17.86_X110.1</v>
       </c>
       <c r="B51" t="str">
         <v>wire</v>
@@ -2482,16 +2482,16 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G51" t="str">
         <v>ea</v>
       </c>
       <c r="H51" t="str">
-        <v>14 AWG</v>
+        <v/>
       </c>
       <c r="I51" t="str">
-        <v>YE</v>
+        <v>VT</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2503,12 +2503,12 @@
         <v/>
       </c>
       <c r="M51" t="str">
-        <v>PBCtrl.2_Caliper.2</v>
+        <v>CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1; K17.86_X110.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PBCtrl.3_X98.1</v>
+        <v>RearDtsch12-M.1_PWR.Gnd</v>
       </c>
       <c r="B52" t="str">
         <v>wire</v>
@@ -2529,7 +2529,7 @@
         <v>ea</v>
       </c>
       <c r="H52" t="str">
-        <v>14 AWG</v>
+        <v>20 AWG</v>
       </c>
       <c r="I52" t="str">
         <v>BK</v>
@@ -2544,12 +2544,12 @@
         <v/>
       </c>
       <c r="M52" t="str">
-        <v>PBCtrl.3_X98.1</v>
+        <v>RearDtsch12-M.1_PWR.Gnd</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1; K17.86_X110.1</v>
+        <v>CtrlRelay.4_EC1.2</v>
       </c>
       <c r="B53" t="str">
         <v>wire</v>
@@ -2564,16 +2564,16 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G53" t="str">
         <v>ea</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>14 AWG</v>
       </c>
       <c r="I53" t="str">
-        <v>VT</v>
+        <v>GNBU</v>
       </c>
       <c r="J53" t="str">
         <v/>
@@ -2585,12 +2585,12 @@
         <v/>
       </c>
       <c r="M53" t="str">
-        <v>CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1; K17.86_X110.1</v>
+        <v>CtrlRelay.4_EC1.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>RearDtsch12-M.1_PWR.Gnd</v>
+        <v>CtrlRelay.10_EC1.5</v>
       </c>
       <c r="B54" t="str">
         <v>wire</v>
@@ -2611,10 +2611,10 @@
         <v>ea</v>
       </c>
       <c r="H54" t="str">
-        <v>20 AWG</v>
+        <v>16 AWG</v>
       </c>
       <c r="I54" t="str">
-        <v>BK</v>
+        <v>GNBK</v>
       </c>
       <c r="J54" t="str">
         <v/>
@@ -2626,12 +2626,12 @@
         <v/>
       </c>
       <c r="M54" t="str">
-        <v>RearDtsch12-M.1_PWR.Gnd</v>
+        <v>CtrlRelay.10_EC1.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>CtrlRelay.4_EC1.2</v>
+        <v>CtrlRelay.1_EC1.3</v>
       </c>
       <c r="B55" t="str">
         <v>wire</v>
@@ -2655,7 +2655,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I55" t="str">
-        <v>GNBU</v>
+        <v>GN</v>
       </c>
       <c r="J55" t="str">
         <v/>
@@ -2667,12 +2667,12 @@
         <v/>
       </c>
       <c r="M55" t="str">
-        <v>CtrlRelay.4_EC1.2</v>
+        <v>CtrlRelay.1_EC1.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>CtrlRelay.10_EC1.5</v>
+        <v>CtrlRelay.5_EC1.6</v>
       </c>
       <c r="B56" t="str">
         <v>wire</v>
@@ -2696,7 +2696,7 @@
         <v>16 AWG</v>
       </c>
       <c r="I56" t="str">
-        <v>GNBK</v>
+        <v>GNYE</v>
       </c>
       <c r="J56" t="str">
         <v/>
@@ -2708,12 +2708,12 @@
         <v/>
       </c>
       <c r="M56" t="str">
-        <v>CtrlRelay.10_EC1.5</v>
+        <v>CtrlRelay.5_EC1.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>CtrlRelay.1_EC1.3</v>
+        <v>EC1.4_CDLLED.2</v>
       </c>
       <c r="B57" t="str">
         <v>wire</v>
@@ -2734,10 +2734,10 @@
         <v>ea</v>
       </c>
       <c r="H57" t="str">
-        <v>14 AWG</v>
+        <v/>
       </c>
       <c r="I57" t="str">
-        <v>GN</v>
+        <v>WHBK</v>
       </c>
       <c r="J57" t="str">
         <v/>
@@ -2749,12 +2749,12 @@
         <v/>
       </c>
       <c r="M57" t="str">
-        <v>CtrlRelay.1_EC1.3</v>
+        <v>EC1.4_CDLLED.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>CtrlRelay.5_EC1.6</v>
+        <v>CDLSw.1_CtrlRelay.7</v>
       </c>
       <c r="B58" t="str">
         <v>wire</v>
@@ -2775,10 +2775,10 @@
         <v>ea</v>
       </c>
       <c r="H58" t="str">
-        <v>16 AWG</v>
+        <v/>
       </c>
       <c r="I58" t="str">
-        <v>GNYE</v>
+        <v>BKRD</v>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -2790,12 +2790,12 @@
         <v/>
       </c>
       <c r="M58" t="str">
-        <v>CtrlRelay.5_EC1.6</v>
+        <v>CDLSw.1_CtrlRelay.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>EC1.4_CDLLED.2</v>
+        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
       </c>
       <c r="B59" t="str">
         <v>wire</v>
@@ -2819,7 +2819,7 @@
         <v/>
       </c>
       <c r="I59" t="str">
-        <v>WHBK</v>
+        <v>OGRD</v>
       </c>
       <c r="J59" t="str">
         <v/>
@@ -2831,27 +2831,27 @@
         <v/>
       </c>
       <c r="M59" t="str">
-        <v>EC1.4_CDLLED.2</v>
+        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>CDLSw.1_CtrlRelay.7</v>
+        <v>10863985</v>
       </c>
       <c r="B60" t="str">
-        <v>wire</v>
+        <v>contact</v>
       </c>
       <c r="C60" t="str">
-        <v>Unassigned</v>
+        <v>10863985</v>
       </c>
       <c r="D60" t="str">
-        <v/>
+        <v>Aptiv</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="G60" t="str">
         <v>ea</v>
@@ -2860,7 +2860,7 @@
         <v/>
       </c>
       <c r="I60" t="str">
-        <v>BKRD</v>
+        <v/>
       </c>
       <c r="J60" t="str">
         <v/>
@@ -2872,94 +2872,12 @@
         <v/>
       </c>
       <c r="M60" t="str">
-        <v>CDLSw.1_CtrlRelay.7</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
-      </c>
-      <c r="B61" t="str">
-        <v>wire</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Unassigned</v>
-      </c>
-      <c r="D61" t="str">
-        <v/>
-      </c>
-      <c r="E61" t="str">
-        <v/>
-      </c>
-      <c r="F61" t="str">
-        <v>1</v>
-      </c>
-      <c r="G61" t="str">
-        <v>ea</v>
-      </c>
-      <c r="H61" t="str">
-        <v/>
-      </c>
-      <c r="I61" t="str">
-        <v>OGRD</v>
-      </c>
-      <c r="J61" t="str">
-        <v/>
-      </c>
-      <c r="K61" t="str">
-        <v/>
-      </c>
-      <c r="L61" t="str">
-        <v/>
-      </c>
-      <c r="M61" t="str">
-        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>10863985</v>
-      </c>
-      <c r="B62" t="str">
-        <v>contact</v>
-      </c>
-      <c r="C62" t="str">
-        <v>10863985</v>
-      </c>
-      <c r="D62" t="str">
-        <v>Aptiv</v>
-      </c>
-      <c r="E62" t="str">
-        <v/>
-      </c>
-      <c r="F62" t="str">
-        <v>37</v>
-      </c>
-      <c r="G62" t="str">
-        <v>ea</v>
-      </c>
-      <c r="H62" t="str">
-        <v/>
-      </c>
-      <c r="I62" t="str">
-        <v/>
-      </c>
-      <c r="J62" t="str">
-        <v/>
-      </c>
-      <c r="K62" t="str">
-        <v/>
-      </c>
-      <c r="L62" t="str">
-        <v/>
-      </c>
-      <c r="M62" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M60"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3019,7 +2937,7 @@
         <v>Total Wires</v>
       </c>
       <c r="B9">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -3035,7 +2953,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>6/2/2026, 11:56:21 AM</v>
+        <v>6/2/2026, 12:32:49 PM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; DashDisplay; DCDC-F; DCDC-R; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F23; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X61; X62; X63; X64; X65; X67; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; X106; X107; X108; X109; X110; X111; X112; X113; ZombieDisplay</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; DashDisplay; DCDC-F; DCDC-R; Dimmer; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F23; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; MgRideL; MgRideR; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; Term; VSS; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X61; X62; X63; X64; X65; X67; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; X106; X107; X108; X109; X110; X111; X112; X113; ZombieDisplay</v>
       </c>
       <c r="B10" t="str">
         <v>connector</v>
@@ -801,7 +801,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G10" t="str">
         <v>ea</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; Bat+.10_K12.30; K12.87_F12.IN</v>
+        <v>Bat+.1_X53; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; Bat+.10_K12.30; K12.87_F12.IN</v>
       </c>
       <c r="B22" t="str">
         <v>wire</v>
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="M22" t="str">
-        <v>Bat+.10_K12.30; Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; K12.87_F12.IN</v>
+        <v>Bat+.10_K12.30; Bat+.1_X53; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; K12.87_F12.IN</v>
       </c>
     </row>
     <row r="23">
@@ -1401,7 +1401,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>FrontDtsch12-M.1_DCDC-F.1; FrontDtsch12-M.1_DCDC-F.1; Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.2_K18.85</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DashDisplay.2; Gnd.2_X61; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; GndCtrl.2_K18.85</v>
       </c>
       <c r="B25" t="str">
         <v>wire</v>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="M25" t="str">
-        <v>FrontDtsch12-M.1_DCDC-F.1; Gnd.1_X93.1; Gnd.2_K13.85; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_K16.85; GndCtrl.2_K18.85</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DashDisplay.2; Gnd.2_X61; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; GndCtrl.2_K18.85</v>
       </c>
     </row>
     <row r="26">
@@ -1483,7 +1483,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K19.85_X101.1; K20.85_X102.1; MitsuCtrl.10_X111.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DashDisplay.2; Gnd.2_X61; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K19.85_X101.1; K20.85_X102.1; MitsuCtrl.10_X111.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
       <c r="B27" t="str">
         <v>wire</v>
@@ -1498,7 +1498,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G27" t="str">
         <v>ea</v>
@@ -1519,12 +1519,12 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K19.85_X101.1; K20.85_X102.1; MitsuCtrl.10_X111.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DashDisplay.2; Gnd.2_X61; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K19.85_X101.1; K20.85_X102.1; MitsuCtrl.10_X111.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>F13.OUT_OilPump.5; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>DashDisplay.8_VSS.Signal; F13.OUT_OilPump.5; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1539,7 +1539,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" t="str">
         <v>ea</v>
@@ -1560,12 +1560,12 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>F13.OUT_OilPump.5; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>DashDisplay.8_VSS.Signal; F13.OUT_OilPump.5; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_DashDisplay.6; PBCtrl.7_DashDisplay.6; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B29" t="str">
         <v>wire</v>
@@ -1580,7 +1580,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29" t="str">
         <v>ea</v>
@@ -1601,7 +1601,7 @@
         <v/>
       </c>
       <c r="M29" t="str">
-        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_GrnLed.1; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_DashDisplay.6; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="30">
@@ -1647,7 +1647,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>FrontDtsch12-F.5_RearDtsch12-F.5</v>
+        <v>DashDisplay.9_MgRideL.Out+; DashDisplay.10_MgRideR.Out+; FrontDtsch12-F.5_RearDtsch12-F.5</v>
       </c>
       <c r="B31" t="str">
         <v>wire</v>
@@ -1662,7 +1662,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" t="str">
         <v>ea</v>
@@ -1683,7 +1683,7 @@
         <v/>
       </c>
       <c r="M31" t="str">
-        <v>FrontDtsch12-F.5_RearDtsch12-F.5</v>
+        <v>DashDisplay.10_MgRideR.Out+; DashDisplay.9_MgRideL.Out+; FrontDtsch12-F.5_RearDtsch12-F.5</v>
       </c>
     </row>
     <row r="32">
@@ -1729,7 +1729,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_PkBrk.1</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_DashDisplay.5</v>
       </c>
       <c r="B33" t="str">
         <v>wire</v>
@@ -1765,12 +1765,12 @@
         <v/>
       </c>
       <c r="M33" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_PkBrk.1</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_DashDisplay.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>FrontDtsch12-F.8_RearDtsch12-F.8</v>
+        <v>FrontDtsch12-F.8_RearDtsch12-F.8; PBCtrl.5_DashDisplay.5</v>
       </c>
       <c r="B34" t="str">
         <v>wire</v>
@@ -1785,7 +1785,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="str">
         <v>ea</v>
@@ -1806,7 +1806,7 @@
         <v/>
       </c>
       <c r="M34" t="str">
-        <v>FrontDtsch12-F.8_RearDtsch12-F.8</v>
+        <v>FrontDtsch12-F.8_RearDtsch12-F.8; PBCtrl.5_DashDisplay.5</v>
       </c>
     </row>
     <row r="35">
@@ -1893,7 +1893,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>F12.OUT_MitsuCtrl.8; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K12.85_X113.1; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>Bat+.1_X53; F12.OUT_MitsuCtrl.8; F21.Out_DashDisplay; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K12.85_X113.1; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_DashDisplay.7; PBCtrl.8_DashDisplay.7; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
       <c r="B37" t="str">
         <v>wire</v>
@@ -1908,7 +1908,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G37" t="str">
         <v>ea</v>
@@ -1929,7 +1929,7 @@
         <v/>
       </c>
       <c r="M37" t="str">
-        <v>F12.OUT_MitsuCtrl.8; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K12.85_X113.1; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_RedLed.1; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>Bat+.1_X53; F12.OUT_MitsuCtrl.8; F21.Out_DashDisplay; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K12.85_X113.1; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_DashDisplay.7; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
     </row>
     <row r="38">
@@ -2262,7 +2262,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; DashDisplay.13_Dimmer.Signal; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B46" t="str">
         <v>wire</v>
@@ -2277,7 +2277,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G46" t="str">
         <v>ea</v>
@@ -2298,12 +2298,12 @@
         <v/>
       </c>
       <c r="M46" t="str">
-        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; DashDisplay.13_Dimmer.Signal; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
+        <v>Gnd.1_DashDisplay.2; OilPump.6_X1.30</v>
       </c>
       <c r="B47" t="str">
         <v>wire</v>
@@ -2339,7 +2339,7 @@
         <v/>
       </c>
       <c r="M47" t="str">
-        <v>Gnd.1_X93.1; OilPump.6_X1.30</v>
+        <v>Gnd.1_DashDisplay.2; OilPump.6_X1.30</v>
       </c>
     </row>
     <row r="48">
@@ -2467,7 +2467,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1; K17.86_X110.1</v>
+        <v>CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K17.86_X110.1</v>
       </c>
       <c r="B51" t="str">
         <v>wire</v>
@@ -2482,7 +2482,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G51" t="str">
         <v>ea</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="M51" t="str">
-        <v>CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F23.IN_X105.1; K17.86_X110.1</v>
+        <v>CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K17.86_X110.1</v>
       </c>
     </row>
     <row r="52">
@@ -2953,7 +2953,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>6/2/2026, 12:32:49 PM</v>
+        <v>6/2/2026, 2:58:32 PM</v>
       </c>
     </row>
   </sheetData>

--- a/wiring/rendered/EVJ-55_plan_bom.xlsx
+++ b/wiring/rendered/EVJ-55_plan_bom.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M70"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -458,16 +458,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>MitsuCtrl</v>
+        <v>CtrlRelay</v>
       </c>
       <c r="B2" t="str">
         <v>connector</v>
       </c>
       <c r="C2" t="str">
-        <v>6189-1092 13-WAY CONNECTOR KIT Inc Terminals &amp; seals [13-AC001</v>
+        <v>89531-60010</v>
       </c>
       <c r="D2" t="str">
-        <v>Sumitomo</v>
+        <v>Toyota</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -485,7 +485,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -499,16 +499,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CtrlRelay</v>
+        <v>X3</v>
       </c>
       <c r="B3" t="str">
         <v>connector</v>
       </c>
       <c r="C3" t="str">
-        <v>89531-60010</v>
+        <v>90980-12326</v>
       </c>
       <c r="D3" t="str">
-        <v>Toyota</v>
+        <v>Sumitomo</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -540,13 +540,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>X3</v>
+        <v>MG1R; MG2R</v>
       </c>
       <c r="B4" t="str">
         <v>connector</v>
       </c>
       <c r="C4" t="str">
-        <v>90980-12326</v>
+        <v>90980-12520</v>
       </c>
       <c r="D4" t="str">
         <v>Sumitomo</v>
@@ -555,7 +555,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="str">
         <v>ea</v>
@@ -567,7 +567,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -581,22 +581,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>X5; X6</v>
+        <v>X1</v>
       </c>
       <c r="B5" t="str">
         <v>connector</v>
       </c>
       <c r="C5" t="str">
-        <v>90980-12520</v>
+        <v>13669859</v>
       </c>
       <c r="D5" t="str">
-        <v>Sumitomo</v>
+        <v>Aptiv</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="str">
         <v>ea</v>
@@ -608,7 +608,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -622,13 +622,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>X1</v>
+        <v>J1</v>
       </c>
       <c r="B6" t="str">
         <v>connector</v>
       </c>
       <c r="C6" t="str">
-        <v>13669859</v>
+        <v>33511394</v>
       </c>
       <c r="D6" t="str">
         <v>Aptiv</v>
@@ -663,16 +663,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>J1</v>
+        <v>Dilong_AC</v>
       </c>
       <c r="B7" t="str">
         <v>connector</v>
       </c>
       <c r="C7" t="str">
-        <v>33511394</v>
+        <v>HS25BCS</v>
       </c>
       <c r="D7" t="str">
-        <v>Aptiv</v>
+        <v>SWS</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -690,7 +690,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -745,7 +745,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>X4</v>
+        <v>Inverter</v>
       </c>
       <c r="B9" t="str">
         <v>connector</v>
@@ -786,22 +786,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; DashDisplay; DCDC-F; DCDC-R; Dimmer; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F21; F23; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; MgRideL; MgRideR; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; Term; VSS; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X61; X62; X63; X64; X65; X67; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X96; X97; X98; X99; X100; X101; X102; X103; X104; X105; X106; X107; X108; X109; X110; X111; X112; X113; ZombieDisplay</v>
+        <v>Dilong_HV</v>
       </c>
       <c r="B10" t="str">
         <v>connector</v>
       </c>
       <c r="C10" t="str">
-        <v>Unassigned</v>
+        <v>MCP 6.3/4.8K, CONTACT, SWS 1241418-4</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>Amp</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="G10" t="str">
         <v>ea</v>
@@ -813,7 +813,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -827,10 +827,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>X2.1_X1.45</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; DashDisplay; DCDC-F; DCDC-R; Dimmer; EB2; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F20; F21; F23; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; MgRideL; MgRideR; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; Pumps; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; ShiftConn; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X61; X62; X63; X64; X65; X67; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X98; X100; X101; X102; X104; X105; X106; X107; X108; X109; X110; X113; X114; X115; X116; X117; X118; X119; X120; X124; X125; X126; ZombieDisplay</v>
       </c>
       <c r="B11" t="str">
-        <v>wire</v>
+        <v>connector</v>
       </c>
       <c r="C11" t="str">
         <v>Unassigned</v>
@@ -842,19 +842,19 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="G11" t="str">
         <v>ea</v>
       </c>
       <c r="H11" t="str">
-        <v>20 AWG</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>YEBU</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>14</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -863,12 +863,12 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>X2.1_X1.45</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>J1.46_X2.2</v>
+        <v>X2.1_X1.45</v>
       </c>
       <c r="B12" t="str">
         <v>wire</v>
@@ -892,7 +892,7 @@
         <v>20 AWG</v>
       </c>
       <c r="I12" t="str">
-        <v>BNBU</v>
+        <v>YEBU</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -904,12 +904,12 @@
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>J1.46_X2.2</v>
+        <v>X2.1_X1.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>X2.5_X1.47</v>
+        <v>J1.46_X2.2</v>
       </c>
       <c r="B13" t="str">
         <v>wire</v>
@@ -933,7 +933,7 @@
         <v>20 AWG</v>
       </c>
       <c r="I13" t="str">
-        <v>WHBU</v>
+        <v>BNBU</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -945,12 +945,12 @@
         <v/>
       </c>
       <c r="M13" t="str">
-        <v>X2.5_X1.47</v>
+        <v>J1.46_X2.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>J1.48_X2.3</v>
+        <v>X2.5_X1.47</v>
       </c>
       <c r="B14" t="str">
         <v>wire</v>
@@ -974,7 +974,7 @@
         <v>20 AWG</v>
       </c>
       <c r="I14" t="str">
-        <v>WHGN</v>
+        <v>WHBU</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -986,12 +986,12 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>J1.48_X2.3</v>
+        <v>X2.5_X1.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>InDtsch12-M.5_K12.86; InDtsch12-M.5_K12.86; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
+        <v>J1.48_X2.3</v>
       </c>
       <c r="B15" t="str">
         <v>wire</v>
@@ -1006,16 +1006,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G15" t="str">
         <v>ea</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>20 AWG</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>WHGN</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -1027,12 +1027,12 @@
         <v/>
       </c>
       <c r="M15" t="str">
-        <v>InDtsch12-M.5_K12.86; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; PBCtrl.6_GrnLed.2; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
+        <v>J1.48_X2.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>J1.16_X4.34; J1.18_X4.13; J1.20_X4.2; J1.22_X4.22; X4.17_X5.3; X6.3_X4.38</v>
+        <v>CtrlRelay.3_EB2.+12V; InDtsch12-M.5_X1.4; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; K12.85_X120.1; K12.85_X120.1; K12.86_X117.1; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
       </c>
       <c r="B16" t="str">
         <v>wire</v>
@@ -1047,16 +1047,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G16" t="str">
         <v>ea</v>
       </c>
       <c r="H16" t="str">
-        <v>22 AWG</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>WH</v>
+        <v/>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1068,12 +1068,12 @@
         <v/>
       </c>
       <c r="M16" t="str">
-        <v>J1.16_X4.34; J1.18_X4.13; J1.20_X4.2; J1.22_X4.22; X4.17_X5.3; X6.3_X4.38</v>
+        <v>CtrlRelay.3_EB2.+12V; InDtsch12-M.5_X1.4; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; K12.85_X120.1; K12.86_X117.1; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>J1.17_X4.35; J1.19_X4.14; J1.21_X4.3; J1.23_X4.23; X4.20_X5.1; X6.1_X4.40</v>
+        <v>Inverter.17_MG1R.3; J1.16_Inverter.34; J1.18_Inverter.13; J1.20_Inverter.2; J1.22_Inverter.22; MG2R.3_Inverter.38</v>
       </c>
       <c r="B17" t="str">
         <v>wire</v>
@@ -1097,7 +1097,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I17" t="str">
-        <v>BK</v>
+        <v>WH</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1109,12 +1109,12 @@
         <v/>
       </c>
       <c r="M17" t="str">
-        <v>J1.17_X4.35; J1.19_X4.14; J1.21_X4.3; J1.23_X4.23; X4.20_X5.1; X6.1_X4.40</v>
+        <v>Inverter.17_MG1R.3; J1.16_Inverter.34; J1.18_Inverter.13; J1.20_Inverter.2; J1.22_Inverter.22; MG2R.3_Inverter.38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>X4.18_X5.2; X6.2_X4.39</v>
+        <v>Inverter.20_MG1R.1; J1.17_Inverter.35; J1.19_Inverter.14; J1.21_Inverter.3; J1.23_Inverter.23; MG2R.1_Inverter.40</v>
       </c>
       <c r="B18" t="str">
         <v>wire</v>
@@ -1129,7 +1129,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G18" t="str">
         <v>ea</v>
@@ -1138,7 +1138,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I18" t="str">
-        <v>BU</v>
+        <v>BK</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1150,12 +1150,12 @@
         <v/>
       </c>
       <c r="M18" t="str">
-        <v>X4.18_X5.2; X6.2_X4.39</v>
+        <v>Inverter.20_MG1R.1; J1.17_Inverter.35; J1.19_Inverter.14; J1.21_Inverter.3; J1.23_Inverter.23; MG2R.1_Inverter.40</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>X4.9_X5.5; X6.5_X4.27</v>
+        <v>Inverter.18_MG1R.2; MG2R.2_Inverter.39</v>
       </c>
       <c r="B19" t="str">
         <v>wire</v>
@@ -1179,7 +1179,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I19" t="str">
-        <v>GN</v>
+        <v>BU</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1191,12 +1191,12 @@
         <v/>
       </c>
       <c r="M19" t="str">
-        <v>X4.9_X5.5; X6.5_X4.27</v>
+        <v>Inverter.18_MG1R.2; MG2R.2_Inverter.39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>X4.7_X5.6; X6.6_X4.29</v>
+        <v>Inverter.9_MG1R.5; MG2R.5_Inverter.27</v>
       </c>
       <c r="B20" t="str">
         <v>wire</v>
@@ -1220,7 +1220,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I20" t="str">
-        <v>RD</v>
+        <v>GN</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1232,12 +1232,12 @@
         <v/>
       </c>
       <c r="M20" t="str">
-        <v>X4.7_X5.6; X6.6_X4.29</v>
+        <v>Inverter.9_MG1R.5; MG2R.5_Inverter.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>X4.6_X5.7; X6.7_X4.28</v>
+        <v>Inverter.7_MG1R.6; MG2R.6_Inverter.29</v>
       </c>
       <c r="B21" t="str">
         <v>wire</v>
@@ -1261,7 +1261,7 @@
         <v>22 AWG</v>
       </c>
       <c r="I21" t="str">
-        <v>YE</v>
+        <v>RD</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1273,12 +1273,12 @@
         <v/>
       </c>
       <c r="M21" t="str">
-        <v>X4.6_X5.7; X6.7_X4.28</v>
+        <v>Inverter.7_MG1R.6; MG2R.6_Inverter.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Bat+.1_X53; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; Bat+.10_K12.30; K12.87_F12.IN</v>
+        <v>Inverter.6_MG1R.7; MG2R.7_Inverter.28</v>
       </c>
       <c r="B22" t="str">
         <v>wire</v>
@@ -1293,16 +1293,16 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G22" t="str">
         <v>ea</v>
       </c>
       <c r="H22" t="str">
-        <v>14 AWG</v>
+        <v>22 AWG</v>
       </c>
       <c r="I22" t="str">
-        <v>RD</v>
+        <v>YE</v>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1314,12 +1314,12 @@
         <v/>
       </c>
       <c r="M22" t="str">
-        <v>Bat+.10_K12.30; Bat+.1_X53; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; K12.87_F12.IN</v>
+        <v>Inverter.6_MG1R.7; MG2R.7_Inverter.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
+        <v>Bat+.1_X53; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; Bat+.10_K12.30; F20.In_Pumps.1</v>
       </c>
       <c r="B23" t="str">
         <v>wire</v>
@@ -1334,7 +1334,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G23" t="str">
         <v>ea</v>
@@ -1343,7 +1343,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>RD</v>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1355,12 +1355,12 @@
         <v/>
       </c>
       <c r="M23" t="str">
-        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
+        <v>Bat+.10_K12.30; Bat+.1_X53; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; F20.In_Pumps.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
+        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
       </c>
       <c r="B24" t="str">
         <v>wire</v>
@@ -1375,16 +1375,16 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G24" t="str">
         <v>ea</v>
       </c>
       <c r="H24" t="str">
-        <v>18 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I24" t="str">
-        <v>VT</v>
+        <v/>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1396,12 +1396,12 @@
         <v/>
       </c>
       <c r="M24" t="str">
-        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
+        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>FrontDtsch12-M.1_DCDC-F.1; FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DashDisplay.2; Gnd.2_X61; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; GndCtrl.2_K18.85</v>
+        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
       </c>
       <c r="B25" t="str">
         <v>wire</v>
@@ -1416,7 +1416,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G25" t="str">
         <v>ea</v>
@@ -1425,7 +1425,7 @@
         <v>18 AWG</v>
       </c>
       <c r="I25" t="str">
-        <v>BK</v>
+        <v>VT</v>
       </c>
       <c r="J25" t="str">
         <v/>
@@ -1437,12 +1437,12 @@
         <v/>
       </c>
       <c r="M25" t="str">
-        <v>FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DashDisplay.2; Gnd.2_X61; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; GndCtrl.2_K18.85</v>
+        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DashDisplay.2; Gnd.2_X114.1; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; GndCtrl.2_K18.85</v>
       </c>
       <c r="B26" t="str">
         <v>wire</v>
@@ -1457,7 +1457,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G26" t="str">
         <v>ea</v>
@@ -1466,7 +1466,7 @@
         <v>18 AWG</v>
       </c>
       <c r="I26" t="str">
-        <v>RD</v>
+        <v>BK</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -1478,12 +1478,12 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DashDisplay.2; Gnd.2_X114.1; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; GndCtrl.2_K18.85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DashDisplay.2; Gnd.2_X61; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K19.85_X101.1; K20.85_X102.1; MitsuCtrl.10_X111.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>F13.OUT_F12.OUT; K12.87_F12.IN</v>
       </c>
       <c r="B27" t="str">
         <v>wire</v>
@@ -1498,16 +1498,16 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G27" t="str">
         <v>ea</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>12 AWG</v>
       </c>
       <c r="I27" t="str">
-        <v>BK</v>
+        <v>RD</v>
       </c>
       <c r="J27" t="str">
         <v/>
@@ -1519,12 +1519,12 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DashDisplay.2; Gnd.2_X61; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K19.85_X101.1; K20.85_X102.1; MitsuCtrl.10_X111.1; PBCtrl.6_GrnLed.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>F13.OUT_F12.OUT; K12.87_F12.IN</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>DashDisplay.8_VSS.Signal; F13.OUT_OilPump.5; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86; EB2.+12v_DashDisplay.1</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1539,16 +1539,16 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G28" t="str">
         <v>ea</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>18 AWG</v>
       </c>
       <c r="I28" t="str">
-        <v>WH</v>
+        <v>RD</v>
       </c>
       <c r="J28" t="str">
         <v/>
@@ -1560,12 +1560,12 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>DashDisplay.8_VSS.Signal; F13.OUT_OilPump.5; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86; EB2.+12v_DashDisplay.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_DashDisplay.6; PBCtrl.7_DashDisplay.6; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DashDisplay.2; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X120.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.6_PkBrk.2; PBCtrl.6_PkBrk.2; PBCtrl.6_PkBrk.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
       <c r="B29" t="str">
         <v>wire</v>
@@ -1580,7 +1580,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G29" t="str">
         <v>ea</v>
@@ -1589,7 +1589,7 @@
         <v/>
       </c>
       <c r="I29" t="str">
-        <v>GN</v>
+        <v>BK</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -1601,12 +1601,12 @@
         <v/>
       </c>
       <c r="M29" t="str">
-        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_DashDisplay.6; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DashDisplay.2; Gnd.3_X61; Gnd.4_X61; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X120.1; K19.85_X101.1; K20.85_X102.1; PBCtrl.6_PkBrk.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
+        <v>F13.OUT_F12.OUT; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
       <c r="B30" t="str">
         <v>wire</v>
@@ -1621,7 +1621,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G30" t="str">
         <v>ea</v>
@@ -1630,7 +1630,7 @@
         <v/>
       </c>
       <c r="I30" t="str">
-        <v>WHBU</v>
+        <v>WH</v>
       </c>
       <c r="J30" t="str">
         <v/>
@@ -1642,12 +1642,12 @@
         <v/>
       </c>
       <c r="M30" t="str">
-        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
+        <v>F13.OUT_F12.OUT; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_ZombieDisplay.3; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>DashDisplay.9_MgRideL.Out+; DashDisplay.10_MgRideR.Out+; FrontDtsch12-F.5_RearDtsch12-F.5</v>
+        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_DashDisplay.6; PBCtrl.7_DashDisplay.6; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B31" t="str">
         <v>wire</v>
@@ -1662,7 +1662,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G31" t="str">
         <v>ea</v>
@@ -1671,7 +1671,7 @@
         <v/>
       </c>
       <c r="I31" t="str">
-        <v>BU</v>
+        <v>GN</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1683,12 +1683,12 @@
         <v/>
       </c>
       <c r="M31" t="str">
-        <v>DashDisplay.10_MgRideR.Out+; DashDisplay.9_MgRideL.Out+; FrontDtsch12-F.5_RearDtsch12-F.5</v>
+        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_X1.27; PBCtrl.7_DashDisplay.6; PRNDL.4_ZombieDisplay.4; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
+        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
       </c>
       <c r="B32" t="str">
         <v>wire</v>
@@ -1712,7 +1712,7 @@
         <v/>
       </c>
       <c r="I32" t="str">
-        <v>WHBN</v>
+        <v>WHBU</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1724,12 +1724,12 @@
         <v/>
       </c>
       <c r="M32" t="str">
-        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
+        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_DashDisplay.5</v>
+        <v>DashDisplay.9_MgRideL.Out+; DashDisplay.10_MgRideR.Out+; FrontDtsch12-F.5_RearDtsch12-F.5; MG1R.8_X1.29</v>
       </c>
       <c r="B33" t="str">
         <v>wire</v>
@@ -1744,7 +1744,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" t="str">
         <v>ea</v>
@@ -1753,7 +1753,7 @@
         <v/>
       </c>
       <c r="I33" t="str">
-        <v>BN</v>
+        <v>BU</v>
       </c>
       <c r="J33" t="str">
         <v/>
@@ -1765,12 +1765,12 @@
         <v/>
       </c>
       <c r="M33" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_DashDisplay.5</v>
+        <v>DashDisplay.10_MgRideR.Out+; DashDisplay.9_MgRideL.Out+; FrontDtsch12-F.5_RearDtsch12-F.5; MG1R.8_X1.29</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>FrontDtsch12-F.8_RearDtsch12-F.8; PBCtrl.5_DashDisplay.5</v>
+        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
       </c>
       <c r="B34" t="str">
         <v>wire</v>
@@ -1785,7 +1785,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="str">
         <v>ea</v>
@@ -1794,7 +1794,7 @@
         <v/>
       </c>
       <c r="I34" t="str">
-        <v>OG</v>
+        <v>WHBN</v>
       </c>
       <c r="J34" t="str">
         <v/>
@@ -1806,12 +1806,12 @@
         <v/>
       </c>
       <c r="M34" t="str">
-        <v>FrontDtsch12-F.8_RearDtsch12-F.8; PBCtrl.5_DashDisplay.5</v>
+        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_DashDisplay.5</v>
       </c>
       <c r="B35" t="str">
         <v>wire</v>
@@ -1826,7 +1826,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" t="str">
         <v>ea</v>
@@ -1835,7 +1835,7 @@
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>WHOG</v>
+        <v>BN</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -1847,12 +1847,12 @@
         <v/>
       </c>
       <c r="M35" t="str">
-        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_DashDisplay.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
+        <v>FrontDtsch12-F.8_RearDtsch12-F.8; PBCtrl.5_DashDisplay.5</v>
       </c>
       <c r="B36" t="str">
         <v>wire</v>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" t="str">
         <v>ea</v>
@@ -1876,7 +1876,7 @@
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>WHGN</v>
+        <v>OG</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -1888,12 +1888,12 @@
         <v/>
       </c>
       <c r="M36" t="str">
-        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
+        <v>FrontDtsch12-F.8_RearDtsch12-F.8; PBCtrl.5_DashDisplay.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bat+.1_X53; F12.OUT_MitsuCtrl.8; F21.Out_DashDisplay; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K12.85_X113.1; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_DashDisplay.7; PBCtrl.8_DashDisplay.7; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
       </c>
       <c r="B37" t="str">
         <v>wire</v>
@@ -1908,7 +1908,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G37" t="str">
         <v>ea</v>
@@ -1917,7 +1917,7 @@
         <v/>
       </c>
       <c r="I37" t="str">
-        <v>RD</v>
+        <v>WHOG</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -1929,12 +1929,12 @@
         <v/>
       </c>
       <c r="M37" t="str">
-        <v>Bat+.1_X53; F12.OUT_MitsuCtrl.8; F21.Out_DashDisplay; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K12.85_X113.1; K18.86_X100.1; MitsuCtrl.7_X112.1; PBCtrl.8_DashDisplay.7; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
+        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
       </c>
       <c r="B38" t="str">
         <v>wire</v>
@@ -1949,16 +1949,16 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" t="str">
         <v>ea</v>
       </c>
       <c r="H38" t="str">
-        <v>3/0 AWG</v>
+        <v/>
       </c>
       <c r="I38" t="str">
-        <v>OGRD</v>
+        <v>WHGN</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -1970,12 +1970,12 @@
         <v/>
       </c>
       <c r="M38" t="str">
-        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X77.1</v>
+        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
+        <v>Bat+.1_X53; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K18.86_X100.1; MG1R.4_X1.14; PBCtrl.8_DashDisplay.7; PBCtrl.8_DashDisplay.7; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
       <c r="B39" t="str">
         <v>wire</v>
@@ -1990,16 +1990,16 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G39" t="str">
         <v>ea</v>
       </c>
       <c r="H39" t="str">
-        <v>20 AWG</v>
+        <v/>
       </c>
       <c r="I39" t="str">
-        <v>OG</v>
+        <v>RD</v>
       </c>
       <c r="J39" t="str">
         <v/>
@@ -2011,12 +2011,12 @@
         <v/>
       </c>
       <c r="M39" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
+        <v>Bat+.1_X53; FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K18.86_X100.1; MG1R.4_X1.14; PBCtrl.8_DashDisplay.7; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>NET_mnnb3cvb_4</v>
+        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X125.1</v>
       </c>
       <c r="B40" t="str">
         <v>wire</v>
@@ -2031,13 +2031,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40" t="str">
         <v>ea</v>
       </c>
       <c r="H40" t="str">
-        <v>14 AWG</v>
+        <v>3/0 AWG</v>
       </c>
       <c r="I40" t="str">
         <v>OGRD</v>
@@ -2052,12 +2052,12 @@
         <v/>
       </c>
       <c r="M40" t="str">
-        <v>NET_mnnb3cvb_4</v>
+        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X125.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
       </c>
       <c r="B41" t="str">
         <v>wire</v>
@@ -2078,10 +2078,10 @@
         <v>ea</v>
       </c>
       <c r="H41" t="str">
-        <v>16 AWG</v>
+        <v>20 AWG</v>
       </c>
       <c r="I41" t="str">
-        <v>OGRD</v>
+        <v>OG</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -2093,12 +2093,12 @@
         <v/>
       </c>
       <c r="M41" t="str">
-        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>HV DiscFrontF.+_X108.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>NET_mnnb3cvb_4</v>
       </c>
       <c r="B42" t="str">
         <v>wire</v>
@@ -2113,16 +2113,16 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" t="str">
         <v>ea</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>14 AWG</v>
       </c>
       <c r="I42" t="str">
-        <v>OGBK</v>
+        <v>OGRD</v>
       </c>
       <c r="J42" t="str">
         <v/>
@@ -2134,12 +2134,12 @@
         <v/>
       </c>
       <c r="M42" t="str">
-        <v>HV DiscFrontF.+_X108.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>NET_mnnb3cvb_4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
       </c>
       <c r="B43" t="str">
         <v>wire</v>
@@ -2154,16 +2154,16 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G43" t="str">
         <v>ea</v>
       </c>
       <c r="H43" t="str">
-        <v>3/0 AWG</v>
+        <v>16 AWG</v>
       </c>
       <c r="I43" t="str">
-        <v>OGBK</v>
+        <v>OGRD</v>
       </c>
       <c r="J43" t="str">
         <v/>
@@ -2175,12 +2175,12 @@
         <v/>
       </c>
       <c r="M43" t="str">
-        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
+        <v>HV DiscFrontF.+_X126.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
       <c r="B44" t="str">
         <v>wire</v>
@@ -2195,7 +2195,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" t="str">
         <v>ea</v>
@@ -2204,7 +2204,7 @@
         <v/>
       </c>
       <c r="I44" t="str">
-        <v>WHRD</v>
+        <v>OGBK</v>
       </c>
       <c r="J44" t="str">
         <v/>
@@ -2216,12 +2216,12 @@
         <v/>
       </c>
       <c r="M44" t="str">
-        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
+        <v>HV DiscFrontF.+_X126.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
+        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
       <c r="B45" t="str">
         <v>wire</v>
@@ -2236,16 +2236,16 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G45" t="str">
         <v>ea</v>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>3/0 AWG</v>
       </c>
       <c r="I45" t="str">
-        <v>RDWH</v>
+        <v>OGBK</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -2257,12 +2257,12 @@
         <v/>
       </c>
       <c r="M45" t="str">
-        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
+        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; DashDisplay.13_Dimmer.Signal; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
       </c>
       <c r="B46" t="str">
         <v>wire</v>
@@ -2277,7 +2277,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G46" t="str">
         <v>ea</v>
@@ -2286,7 +2286,7 @@
         <v/>
       </c>
       <c r="I46" t="str">
-        <v>YE</v>
+        <v>WHRD</v>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -2298,12 +2298,12 @@
         <v/>
       </c>
       <c r="M46" t="str">
-        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; DashDisplay.13_Dimmer.Signal; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Gnd.1_DashDisplay.2; OilPump.6_X1.30</v>
+        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
       </c>
       <c r="B47" t="str">
         <v>wire</v>
@@ -2324,10 +2324,10 @@
         <v>ea</v>
       </c>
       <c r="H47" t="str">
-        <v>12 AWG</v>
+        <v/>
       </c>
       <c r="I47" t="str">
-        <v>BK</v>
+        <v>RDWH</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -2339,12 +2339,12 @@
         <v/>
       </c>
       <c r="M47" t="str">
-        <v>Gnd.1_DashDisplay.2; OilPump.6_X1.30</v>
+        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>PBCtrl.1_Caliper.1</v>
+        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; DashDisplay.13_Dimmer.Signal; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B48" t="str">
         <v>wire</v>
@@ -2359,16 +2359,16 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G48" t="str">
         <v>ea</v>
       </c>
       <c r="H48" t="str">
-        <v>14 AWG</v>
+        <v/>
       </c>
       <c r="I48" t="str">
-        <v>WH</v>
+        <v>YE</v>
       </c>
       <c r="J48" t="str">
         <v/>
@@ -2380,12 +2380,12 @@
         <v/>
       </c>
       <c r="M48" t="str">
-        <v>PBCtrl.1_Caliper.1</v>
+        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; DashDisplay.13_Dimmer.Signal; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_X1.28; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>PBCtrl.2_Caliper.2</v>
+        <v>Gnd.1_DashDisplay.2; OilPump.6_X1.30</v>
       </c>
       <c r="B49" t="str">
         <v>wire</v>
@@ -2400,16 +2400,16 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="str">
         <v>ea</v>
       </c>
       <c r="H49" t="str">
-        <v>14 AWG</v>
+        <v>12 AWG</v>
       </c>
       <c r="I49" t="str">
-        <v>YE</v>
+        <v>BK</v>
       </c>
       <c r="J49" t="str">
         <v/>
@@ -2421,12 +2421,12 @@
         <v/>
       </c>
       <c r="M49" t="str">
-        <v>PBCtrl.2_Caliper.2</v>
+        <v>Gnd.1_DashDisplay.2; OilPump.6_X1.30</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>PBCtrl.3_X98.1</v>
+        <v>PBCtrl.1_Caliper.1</v>
       </c>
       <c r="B50" t="str">
         <v>wire</v>
@@ -2450,7 +2450,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I50" t="str">
-        <v>BK</v>
+        <v>WH</v>
       </c>
       <c r="J50" t="str">
         <v/>
@@ -2462,12 +2462,12 @@
         <v/>
       </c>
       <c r="M50" t="str">
-        <v>PBCtrl.3_X98.1</v>
+        <v>PBCtrl.1_Caliper.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K17.86_X110.1</v>
+        <v>PBCtrl.2_Caliper.2</v>
       </c>
       <c r="B51" t="str">
         <v>wire</v>
@@ -2482,16 +2482,16 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G51" t="str">
         <v>ea</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>14 AWG</v>
       </c>
       <c r="I51" t="str">
-        <v>VT</v>
+        <v>YE</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2503,12 +2503,12 @@
         <v/>
       </c>
       <c r="M51" t="str">
-        <v>CtrlRelay.3_CDLLED.1; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K17.86_X110.1</v>
+        <v>PBCtrl.2_Caliper.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>RearDtsch12-M.1_PWR.Gnd</v>
+        <v>PBCtrl.3_X98.1</v>
       </c>
       <c r="B52" t="str">
         <v>wire</v>
@@ -2529,7 +2529,7 @@
         <v>ea</v>
       </c>
       <c r="H52" t="str">
-        <v>20 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I52" t="str">
         <v>BK</v>
@@ -2544,12 +2544,12 @@
         <v/>
       </c>
       <c r="M52" t="str">
-        <v>RearDtsch12-M.1_PWR.Gnd</v>
+        <v>PBCtrl.3_X98.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>CtrlRelay.4_EC1.2</v>
+        <v>CtrlRelay.3_EB2.+12V; CtrlRelay.3_EB2.+12V; CtrlRelay.3_EB2.+12V; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K12.86_X117.1; K12.86_X117.1; K17.86_X110.1</v>
       </c>
       <c r="B53" t="str">
         <v>wire</v>
@@ -2564,16 +2564,16 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G53" t="str">
         <v>ea</v>
       </c>
       <c r="H53" t="str">
-        <v>14 AWG</v>
+        <v/>
       </c>
       <c r="I53" t="str">
-        <v>GNBU</v>
+        <v>VT</v>
       </c>
       <c r="J53" t="str">
         <v/>
@@ -2585,12 +2585,12 @@
         <v/>
       </c>
       <c r="M53" t="str">
-        <v>CtrlRelay.4_EC1.2</v>
+        <v>CtrlRelay.3_EB2.+12V; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K12.86_X117.1; K17.86_X110.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>CtrlRelay.10_EC1.5</v>
+        <v>RearDtsch12-M.1_PWR.Gnd</v>
       </c>
       <c r="B54" t="str">
         <v>wire</v>
@@ -2611,10 +2611,10 @@
         <v>ea</v>
       </c>
       <c r="H54" t="str">
-        <v>16 AWG</v>
+        <v>20 AWG</v>
       </c>
       <c r="I54" t="str">
-        <v>GNBK</v>
+        <v>BK</v>
       </c>
       <c r="J54" t="str">
         <v/>
@@ -2626,12 +2626,12 @@
         <v/>
       </c>
       <c r="M54" t="str">
-        <v>CtrlRelay.10_EC1.5</v>
+        <v>RearDtsch12-M.1_PWR.Gnd</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>CtrlRelay.1_EC1.3</v>
+        <v>CtrlRelay.4_EC1.2</v>
       </c>
       <c r="B55" t="str">
         <v>wire</v>
@@ -2655,7 +2655,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I55" t="str">
-        <v>GN</v>
+        <v>GNBU</v>
       </c>
       <c r="J55" t="str">
         <v/>
@@ -2667,12 +2667,12 @@
         <v/>
       </c>
       <c r="M55" t="str">
-        <v>CtrlRelay.1_EC1.3</v>
+        <v>CtrlRelay.4_EC1.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>CtrlRelay.5_EC1.6</v>
+        <v>CtrlRelay.10_EC1.5</v>
       </c>
       <c r="B56" t="str">
         <v>wire</v>
@@ -2696,7 +2696,7 @@
         <v>16 AWG</v>
       </c>
       <c r="I56" t="str">
-        <v>GNYE</v>
+        <v>GNBK</v>
       </c>
       <c r="J56" t="str">
         <v/>
@@ -2708,12 +2708,12 @@
         <v/>
       </c>
       <c r="M56" t="str">
-        <v>CtrlRelay.5_EC1.6</v>
+        <v>CtrlRelay.10_EC1.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>EC1.4_CDLLED.2</v>
+        <v>CtrlRelay.1_EC1.3</v>
       </c>
       <c r="B57" t="str">
         <v>wire</v>
@@ -2734,10 +2734,10 @@
         <v>ea</v>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>14 AWG</v>
       </c>
       <c r="I57" t="str">
-        <v>WHBK</v>
+        <v>GN</v>
       </c>
       <c r="J57" t="str">
         <v/>
@@ -2749,12 +2749,12 @@
         <v/>
       </c>
       <c r="M57" t="str">
-        <v>EC1.4_CDLLED.2</v>
+        <v>CtrlRelay.1_EC1.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>CDLSw.1_CtrlRelay.7</v>
+        <v>CtrlRelay.5_EC1.6</v>
       </c>
       <c r="B58" t="str">
         <v>wire</v>
@@ -2775,10 +2775,10 @@
         <v>ea</v>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>16 AWG</v>
       </c>
       <c r="I58" t="str">
-        <v>BKRD</v>
+        <v>GNYE</v>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -2790,12 +2790,12 @@
         <v/>
       </c>
       <c r="M58" t="str">
-        <v>CDLSw.1_CtrlRelay.7</v>
+        <v>CtrlRelay.5_EC1.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
+        <v>EC1.4_CDLLED.2; Gnd.2_X114.1</v>
       </c>
       <c r="B59" t="str">
         <v>wire</v>
@@ -2810,7 +2810,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="str">
         <v>ea</v>
@@ -2819,7 +2819,7 @@
         <v/>
       </c>
       <c r="I59" t="str">
-        <v>OGRD</v>
+        <v>WHBK</v>
       </c>
       <c r="J59" t="str">
         <v/>
@@ -2831,53 +2831,463 @@
         <v/>
       </c>
       <c r="M59" t="str">
-        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
+        <v>EC1.4_CDLLED.2; Gnd.2_X114.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
+        <v>CDLSw.1_CtrlRelay.7</v>
+      </c>
+      <c r="B60" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>1</v>
+      </c>
+      <c r="G60" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v>BKRD</v>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v>CDLSw.1_CtrlRelay.7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
+      </c>
+      <c r="B61" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>1</v>
+      </c>
+      <c r="G61" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v>OGRD</v>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>DashDisplay.8_EB2.VSS</v>
+      </c>
+      <c r="B62" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>1</v>
+      </c>
+      <c r="G62" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v>GNRD</v>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v>DashDisplay.8_EB2.VSS</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>EB2.+12v_DashDisplay.1</v>
+      </c>
+      <c r="B63" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v>1</v>
+      </c>
+      <c r="G63" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v>BKWH</v>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v>EB2.+12v_DashDisplay.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>MG2R.8_X1.13</v>
+      </c>
+      <c r="B64" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>1</v>
+      </c>
+      <c r="G64" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v>GY</v>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v>MG2R.8_X1.13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>MG2R.4_X1.12</v>
+      </c>
+      <c r="B65" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>1</v>
+      </c>
+      <c r="G65" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v>LI</v>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v>MG2R.4_X1.12</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>ShiftConn.8_X124.1</v>
+      </c>
+      <c r="B66" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>1</v>
+      </c>
+      <c r="G66" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H66" t="str">
+        <v>20 AWG</v>
+      </c>
+      <c r="I66" t="str">
+        <v>RD</v>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v>ShiftConn.8_X124.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>ShiftConn.3_Inverter.25</v>
+      </c>
+      <c r="B67" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v>1</v>
+      </c>
+      <c r="G67" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v>YEOG</v>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v>ShiftConn.3_Inverter.25</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Pos Fuse.IN_X125.1</v>
+      </c>
+      <c r="B68" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>1</v>
+      </c>
+      <c r="G68" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H68" t="str">
+        <v>10 AWG</v>
+      </c>
+      <c r="I68" t="str">
+        <v>RD</v>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v>Pos Fuse.IN_X125.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>HV DiscFrontF.+_X126.1</v>
+      </c>
+      <c r="B69" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>1</v>
+      </c>
+      <c r="G69" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H69" t="str">
+        <v>10 AWG</v>
+      </c>
+      <c r="I69" t="str">
+        <v>BK</v>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v>HV DiscFrontF.+_X126.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
         <v>10863985</v>
       </c>
-      <c r="B60" t="str">
+      <c r="B70" t="str">
         <v>contact</v>
       </c>
-      <c r="C60" t="str">
+      <c r="C70" t="str">
         <v>10863985</v>
       </c>
-      <c r="D60" t="str">
+      <c r="D70" t="str">
         <v>Aptiv</v>
       </c>
-      <c r="E60" t="str">
-        <v/>
-      </c>
-      <c r="F60" t="str">
-        <v>37</v>
-      </c>
-      <c r="G60" t="str">
-        <v>ea</v>
-      </c>
-      <c r="H60" t="str">
-        <v/>
-      </c>
-      <c r="I60" t="str">
-        <v/>
-      </c>
-      <c r="J60" t="str">
-        <v/>
-      </c>
-      <c r="K60" t="str">
-        <v/>
-      </c>
-      <c r="L60" t="str">
-        <v/>
-      </c>
-      <c r="M60" t="str">
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>33</v>
+      </c>
+      <c r="G70" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M70"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2929,7 +3339,7 @@
         <v>Total Connectors</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2937,7 +3347,7 @@
         <v>Total Wires</v>
       </c>
       <c r="B9">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -2953,7 +3363,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>6/2/2026, 2:58:32 PM</v>
+        <v>8/5/2026, 12:29:13 PM</v>
       </c>
     </row>
   </sheetData>
